--- a/excel/analise_projetos_por_senioridade_2021-2026.xlsx
+++ b/excel/analise_projetos_por_senioridade_2021-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Duh\Documents\Analises\team-seniority-analysis\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F4F7454-3572-45F3-88FC-5BED466C871F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B711F5-7693-4152-B55D-AD7253A51EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9B74B778-46C1-4B51-BB64-51BC1E9E92E7}"/>
   </bookViews>
@@ -24,8 +24,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId5"/>
-    <pivotCache cacheId="10" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="26">
   <si>
     <t>ordem_granularidade</t>
   </si>
@@ -126,9 +126,6 @@
     <t>Rótulos de Linha</t>
   </si>
   <si>
-    <t>Total Geral</t>
-  </si>
-  <si>
     <t>Rótulos de Coluna</t>
   </si>
   <si>
@@ -185,7 +182,6 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -194,10 +190,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -205,67 +202,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="46">
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
+  <dxfs count="26">
     <dxf>
       <alignment horizontal="center"/>
     </dxf>
@@ -746,7 +683,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'TB Dinamica Cons. 1'!$A$6:$A$9</c:f>
+              <c:f>'TB Dinamica Cons. 1'!$A$6:$A$8</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -763,7 +700,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'TB Dinamica Cons. 1'!$B$6:$B$9</c:f>
+              <c:f>'TB Dinamica Cons. 1'!$B$6:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -811,7 +748,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'TB Dinamica Cons. 1'!$A$6:$A$9</c:f>
+              <c:f>'TB Dinamica Cons. 1'!$A$6:$A$8</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -828,7 +765,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'TB Dinamica Cons. 1'!$C$6:$C$9</c:f>
+              <c:f>'TB Dinamica Cons. 1'!$C$6:$C$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -876,7 +813,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'TB Dinamica Cons. 1'!$A$6:$A$9</c:f>
+              <c:f>'TB Dinamica Cons. 1'!$A$6:$A$8</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -893,7 +830,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'TB Dinamica Cons. 1'!$D$6:$D$9</c:f>
+              <c:f>'TB Dinamica Cons. 1'!$D$6:$D$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -941,7 +878,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'TB Dinamica Cons. 1'!$A$6:$A$9</c:f>
+              <c:f>'TB Dinamica Cons. 1'!$A$6:$A$8</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -958,7 +895,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'TB Dinamica Cons. 1'!$E$6:$E$9</c:f>
+              <c:f>'TB Dinamica Cons. 1'!$E$6:$E$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -1006,7 +943,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'TB Dinamica Cons. 1'!$A$6:$A$9</c:f>
+              <c:f>'TB Dinamica Cons. 1'!$A$6:$A$8</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -1023,7 +960,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'TB Dinamica Cons. 1'!$F$6:$F$9</c:f>
+              <c:f>'TB Dinamica Cons. 1'!$F$6:$F$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -1071,7 +1008,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'TB Dinamica Cons. 1'!$A$6:$A$9</c:f>
+              <c:f>'TB Dinamica Cons. 1'!$A$6:$A$8</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -1088,7 +1025,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'TB Dinamica Cons. 1'!$G$6:$G$9</c:f>
+              <c:f>'TB Dinamica Cons. 1'!$G$6:$G$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -1718,7 +1655,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'TB Dinamica Cons. 2'!$A$5:$A$8</c:f>
+              <c:f>'TB Dinamica Cons. 2'!$A$5:$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -1735,7 +1672,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'TB Dinamica Cons. 2'!$B$5:$B$8</c:f>
+              <c:f>'TB Dinamica Cons. 2'!$B$5:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -1783,7 +1720,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'TB Dinamica Cons. 2'!$A$5:$A$8</c:f>
+              <c:f>'TB Dinamica Cons. 2'!$A$5:$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -1800,7 +1737,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'TB Dinamica Cons. 2'!$C$5:$C$8</c:f>
+              <c:f>'TB Dinamica Cons. 2'!$C$5:$C$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -1848,7 +1785,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'TB Dinamica Cons. 2'!$A$5:$A$8</c:f>
+              <c:f>'TB Dinamica Cons. 2'!$A$5:$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -1865,7 +1802,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'TB Dinamica Cons. 2'!$D$5:$D$8</c:f>
+              <c:f>'TB Dinamica Cons. 2'!$D$5:$D$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -1913,7 +1850,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'TB Dinamica Cons. 2'!$A$5:$A$8</c:f>
+              <c:f>'TB Dinamica Cons. 2'!$A$5:$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -1930,7 +1867,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'TB Dinamica Cons. 2'!$E$5:$E$8</c:f>
+              <c:f>'TB Dinamica Cons. 2'!$E$5:$E$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -1978,7 +1915,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'TB Dinamica Cons. 2'!$A$5:$A$8</c:f>
+              <c:f>'TB Dinamica Cons. 2'!$A$5:$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -1995,7 +1932,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'TB Dinamica Cons. 2'!$F$5:$F$8</c:f>
+              <c:f>'TB Dinamica Cons. 2'!$F$5:$F$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -2043,7 +1980,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'TB Dinamica Cons. 2'!$A$5:$A$8</c:f>
+              <c:f>'TB Dinamica Cons. 2'!$A$5:$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -2060,7 +1997,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'TB Dinamica Cons. 2'!$G$5:$G$8</c:f>
+              <c:f>'TB Dinamica Cons. 2'!$G$5:$G$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -6163,8 +6100,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C82A6434-207F-4269-B954-C32266593A5D}" name="Tabela dinâmica1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="A4:H9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C82A6434-207F-4269-B954-C32266593A5D}" name="Tabela dinâmica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A4:G8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
     <pivotField axis="axisPage" showAll="0">
@@ -6202,7 +6139,7 @@
   <rowFields count="1">
     <field x="5"/>
   </rowFields>
-  <rowItems count="4">
+  <rowItems count="3">
     <i>
       <x/>
     </i>
@@ -6212,14 +6149,11 @@
     <i>
       <x v="2"/>
     </i>
-    <i t="grand">
-      <x/>
-    </i>
   </rowItems>
   <colFields count="1">
     <field x="3"/>
   </colFields>
-  <colItems count="7">
+  <colItems count="6">
     <i>
       <x/>
     </i>
@@ -6237,9 +6171,6 @@
     </i>
     <i>
       <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
     </i>
   </colItems>
   <pageFields count="1">
@@ -6335,8 +6266,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{24DC186A-E8ED-47C8-8A1B-4634B1FA7F18}" name="Tabela dinâmica2" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
-  <location ref="A3:H8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{24DC186A-E8ED-47C8-8A1B-4634B1FA7F18}" name="Tabela dinâmica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="A3:G7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField axis="axisCol" showAll="0">
       <items count="7">
@@ -6366,7 +6297,7 @@
   <rowFields count="1">
     <field x="2"/>
   </rowFields>
-  <rowItems count="4">
+  <rowItems count="3">
     <i>
       <x/>
     </i>
@@ -6376,14 +6307,11 @@
     <i>
       <x v="2"/>
     </i>
-    <i t="grand">
-      <x/>
-    </i>
   </rowItems>
   <colFields count="1">
     <field x="0"/>
   </colFields>
-  <colItems count="7">
+  <colItems count="6">
     <i>
       <x/>
     </i>
@@ -6402,50 +6330,47 @@
     <i>
       <x v="5"/>
     </i>
-    <i t="grand">
-      <x/>
-    </i>
   </colItems>
   <dataFields count="1">
     <dataField name="Volume de participações ajustado pelo tamanho da categoria" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="10">
-    <format dxfId="39">
+    <format dxfId="19">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="38">
+    <format dxfId="18">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="37">
+    <format dxfId="17">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="36">
+    <format dxfId="16">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="35">
+    <format dxfId="15">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="34">
+    <format dxfId="14">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="33">
+    <format dxfId="13">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="32">
+    <format dxfId="12">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
+    <format dxfId="11">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="30">
+    <format dxfId="10">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -6645,11 +6570,11 @@
   <autoFilter ref="A1:H243" xr:uid="{E6988133-BDD9-4A35-BA88-E5905B408F2C}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{B9663AFE-9F2F-4E01-AB56-32B4E677F7E4}" uniqueName="1" name="ordem_granularidade" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{30C39B33-55CC-4639-9F0B-E49EA26548BB}" uniqueName="2" name="granularidade" queryTableFieldId="2" dataDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{2DB83291-6883-4E5B-8624-A07B59B357BC}" uniqueName="3" name="periodo_inicio" queryTableFieldId="3" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{30C39B33-55CC-4639-9F0B-E49EA26548BB}" uniqueName="2" name="granularidade" queryTableFieldId="2" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{2DB83291-6883-4E5B-8624-A07B59B357BC}" uniqueName="3" name="periodo_inicio" queryTableFieldId="3" dataDxfId="24"/>
     <tableColumn id="4" xr3:uid="{FDCCED38-E2AC-4807-A49E-E99812A0F471}" uniqueName="4" name="ano" queryTableFieldId="4"/>
-    <tableColumn id="5" xr3:uid="{00D820F7-F008-42FD-BC6B-75AD1DAD20D4}" uniqueName="5" name="periodo_status" queryTableFieldId="5" dataDxfId="43"/>
-    <tableColumn id="6" xr3:uid="{819C2292-8041-4763-B155-A9EA7934D098}" uniqueName="6" name="senioridade" queryTableFieldId="6" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{00D820F7-F008-42FD-BC6B-75AD1DAD20D4}" uniqueName="5" name="periodo_status" queryTableFieldId="5" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{819C2292-8041-4763-B155-A9EA7934D098}" uniqueName="6" name="senioridade" queryTableFieldId="6" dataDxfId="22"/>
     <tableColumn id="7" xr3:uid="{BA83831A-26AE-40E4-9C91-BA424710C5D0}" uniqueName="7" name="projetos_distintos" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{79EA0454-4268-48C0-980E-C4333B1D6BC9}" uniqueName="8" name="participacoes" queryTableFieldId="8"/>
   </tableColumns>
@@ -6662,8 +6587,8 @@
   <autoFilter ref="A1:G19" xr:uid="{96BC7407-582F-4FFD-847D-18F0BB29FB30}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{1893FA30-DFBC-4FD9-AD09-BB242B1FF92D}" uniqueName="1" name="ano" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{25225C26-F0B2-4013-B874-BCAFF5497E7C}" uniqueName="2" name="periodo_status" queryTableFieldId="2" dataDxfId="41"/>
-    <tableColumn id="3" xr3:uid="{34352976-065C-40AF-995B-FC5B60C1B562}" uniqueName="3" name="senioridade" queryTableFieldId="3" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{25225C26-F0B2-4013-B874-BCAFF5497E7C}" uniqueName="2" name="periodo_status" queryTableFieldId="2" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{34352976-065C-40AF-995B-FC5B60C1B562}" uniqueName="3" name="senioridade" queryTableFieldId="3" dataDxfId="20"/>
     <tableColumn id="4" xr3:uid="{B187FE6A-F5B1-45F5-B3B1-B174C48C9E40}" uniqueName="4" name="total_participacoes" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{D177902C-F8F0-45EA-BB26-CB2ACF4DF1DB}" uniqueName="5" name="meses_observados" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{6582278A-B095-4DC1-8B6F-BFB98AE7CCC7}" uniqueName="6" name="media_mensal_profissionais_categoria" queryTableFieldId="6"/>
@@ -7033,19 +6958,19 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2">
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1">
         <v>44197</v>
       </c>
       <c r="D2">
         <v>2021</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
         <v>10</v>
       </c>
       <c r="G2">
@@ -7059,19 +6984,19 @@
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2">
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1">
         <v>44197</v>
       </c>
       <c r="D3">
         <v>2021</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
         <v>11</v>
       </c>
       <c r="G3">
@@ -7085,19 +7010,19 @@
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2">
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1">
         <v>44197</v>
       </c>
       <c r="D4">
         <v>2021</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
         <v>12</v>
       </c>
       <c r="G4">
@@ -7111,19 +7036,19 @@
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2">
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1">
         <v>44228</v>
       </c>
       <c r="D5">
         <v>2021</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
         <v>10</v>
       </c>
       <c r="G5">
@@ -7137,19 +7062,19 @@
       <c r="A6">
         <v>1</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2">
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="1">
         <v>44228</v>
       </c>
       <c r="D6">
         <v>2021</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
         <v>11</v>
       </c>
       <c r="G6">
@@ -7163,19 +7088,19 @@
       <c r="A7">
         <v>1</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2">
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1">
         <v>44228</v>
       </c>
       <c r="D7">
         <v>2021</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
         <v>12</v>
       </c>
       <c r="G7">
@@ -7189,19 +7114,19 @@
       <c r="A8">
         <v>1</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2">
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="1">
         <v>44256</v>
       </c>
       <c r="D8">
         <v>2021</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
         <v>10</v>
       </c>
       <c r="G8">
@@ -7215,19 +7140,19 @@
       <c r="A9">
         <v>1</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2">
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="1">
         <v>44256</v>
       </c>
       <c r="D9">
         <v>2021</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="1" t="s">
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
         <v>11</v>
       </c>
       <c r="G9">
@@ -7241,19 +7166,19 @@
       <c r="A10">
         <v>1</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="2">
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="1">
         <v>44256</v>
       </c>
       <c r="D10">
         <v>2021</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="1" t="s">
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
         <v>12</v>
       </c>
       <c r="G10">
@@ -7267,19 +7192,19 @@
       <c r="A11">
         <v>1</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="2">
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="1">
         <v>44287</v>
       </c>
       <c r="D11">
         <v>2021</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="1" t="s">
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
         <v>10</v>
       </c>
       <c r="G11">
@@ -7293,19 +7218,19 @@
       <c r="A12">
         <v>1</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="2">
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="1">
         <v>44287</v>
       </c>
       <c r="D12">
         <v>2021</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="1" t="s">
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
         <v>11</v>
       </c>
       <c r="G12">
@@ -7319,19 +7244,19 @@
       <c r="A13">
         <v>1</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="2">
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="1">
         <v>44287</v>
       </c>
       <c r="D13">
         <v>2021</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="1" t="s">
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
         <v>12</v>
       </c>
       <c r="G13">
@@ -7345,19 +7270,19 @@
       <c r="A14">
         <v>1</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="2">
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="1">
         <v>44317</v>
       </c>
       <c r="D14">
         <v>2021</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="1" t="s">
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
         <v>10</v>
       </c>
       <c r="G14">
@@ -7371,19 +7296,19 @@
       <c r="A15">
         <v>1</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="2">
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="1">
         <v>44317</v>
       </c>
       <c r="D15">
         <v>2021</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="1" t="s">
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
         <v>11</v>
       </c>
       <c r="G15">
@@ -7397,19 +7322,19 @@
       <c r="A16">
         <v>1</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="2">
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="1">
         <v>44317</v>
       </c>
       <c r="D16">
         <v>2021</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="1" t="s">
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
         <v>12</v>
       </c>
       <c r="G16">
@@ -7423,19 +7348,19 @@
       <c r="A17">
         <v>1</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="2">
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="1">
         <v>44348</v>
       </c>
       <c r="D17">
         <v>2021</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="1" t="s">
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
         <v>10</v>
       </c>
       <c r="G17">
@@ -7449,19 +7374,19 @@
       <c r="A18">
         <v>1</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="2">
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="1">
         <v>44348</v>
       </c>
       <c r="D18">
         <v>2021</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="1" t="s">
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
         <v>11</v>
       </c>
       <c r="G18">
@@ -7475,19 +7400,19 @@
       <c r="A19">
         <v>1</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="2">
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="1">
         <v>44348</v>
       </c>
       <c r="D19">
         <v>2021</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="1" t="s">
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
         <v>12</v>
       </c>
       <c r="G19">
@@ -7501,19 +7426,19 @@
       <c r="A20">
         <v>1</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="2">
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="1">
         <v>44378</v>
       </c>
       <c r="D20">
         <v>2021</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="1" t="s">
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
         <v>10</v>
       </c>
       <c r="G20">
@@ -7527,19 +7452,19 @@
       <c r="A21">
         <v>1</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="2">
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="1">
         <v>44378</v>
       </c>
       <c r="D21">
         <v>2021</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="1" t="s">
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
         <v>11</v>
       </c>
       <c r="G21">
@@ -7553,19 +7478,19 @@
       <c r="A22">
         <v>1</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="2">
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="1">
         <v>44378</v>
       </c>
       <c r="D22">
         <v>2021</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" s="1" t="s">
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
         <v>12</v>
       </c>
       <c r="G22">
@@ -7579,19 +7504,19 @@
       <c r="A23">
         <v>1</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="2">
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="1">
         <v>44409</v>
       </c>
       <c r="D23">
         <v>2021</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="1" t="s">
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" t="s">
         <v>10</v>
       </c>
       <c r="G23">
@@ -7605,19 +7530,19 @@
       <c r="A24">
         <v>1</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="2">
+      <c r="B24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="1">
         <v>44440</v>
       </c>
       <c r="D24">
         <v>2021</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" s="1" t="s">
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" t="s">
         <v>10</v>
       </c>
       <c r="G24">
@@ -7631,19 +7556,19 @@
       <c r="A25">
         <v>1</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="2">
+      <c r="B25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="1">
         <v>44470</v>
       </c>
       <c r="D25">
         <v>2021</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" s="1" t="s">
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s">
         <v>10</v>
       </c>
       <c r="G25">
@@ -7657,19 +7582,19 @@
       <c r="A26">
         <v>1</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="2">
+      <c r="B26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="1">
         <v>44470</v>
       </c>
       <c r="D26">
         <v>2021</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" s="1" t="s">
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" t="s">
         <v>11</v>
       </c>
       <c r="G26">
@@ -7683,19 +7608,19 @@
       <c r="A27">
         <v>1</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="2">
+      <c r="B27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="1">
         <v>44470</v>
       </c>
       <c r="D27">
         <v>2021</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" s="1" t="s">
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s">
         <v>12</v>
       </c>
       <c r="G27">
@@ -7709,19 +7634,19 @@
       <c r="A28">
         <v>1</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="2">
+      <c r="B28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="1">
         <v>44501</v>
       </c>
       <c r="D28">
         <v>2021</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" s="1" t="s">
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" t="s">
         <v>10</v>
       </c>
       <c r="G28">
@@ -7735,19 +7660,19 @@
       <c r="A29">
         <v>1</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="2">
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="1">
         <v>44501</v>
       </c>
       <c r="D29">
         <v>2021</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" s="1" t="s">
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" t="s">
         <v>11</v>
       </c>
       <c r="G29">
@@ -7761,19 +7686,19 @@
       <c r="A30">
         <v>1</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="2">
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="1">
         <v>44501</v>
       </c>
       <c r="D30">
         <v>2021</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" s="1" t="s">
+      <c r="E30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" t="s">
         <v>12</v>
       </c>
       <c r="G30">
@@ -7787,19 +7712,19 @@
       <c r="A31">
         <v>1</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="2">
+      <c r="B31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="1">
         <v>44531</v>
       </c>
       <c r="D31">
         <v>2021</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" s="1" t="s">
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s">
         <v>10</v>
       </c>
       <c r="G31">
@@ -7813,19 +7738,19 @@
       <c r="A32">
         <v>1</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="2">
+      <c r="B32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="1">
         <v>44531</v>
       </c>
       <c r="D32">
         <v>2021</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" s="1" t="s">
+      <c r="E32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" t="s">
         <v>11</v>
       </c>
       <c r="G32">
@@ -7839,19 +7764,19 @@
       <c r="A33">
         <v>1</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="2">
+      <c r="B33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="1">
         <v>44531</v>
       </c>
       <c r="D33">
         <v>2021</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" s="1" t="s">
+      <c r="E33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" t="s">
         <v>12</v>
       </c>
       <c r="G33">
@@ -7865,19 +7790,19 @@
       <c r="A34">
         <v>1</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="2">
+      <c r="B34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="1">
         <v>44562</v>
       </c>
       <c r="D34">
         <v>2022</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" s="1" t="s">
+      <c r="E34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" t="s">
         <v>10</v>
       </c>
       <c r="G34">
@@ -7891,19 +7816,19 @@
       <c r="A35">
         <v>1</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="2">
+      <c r="B35" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="1">
         <v>44562</v>
       </c>
       <c r="D35">
         <v>2022</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" s="1" t="s">
+      <c r="E35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" t="s">
         <v>11</v>
       </c>
       <c r="G35">
@@ -7917,19 +7842,19 @@
       <c r="A36">
         <v>1</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="2">
+      <c r="B36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="1">
         <v>44593</v>
       </c>
       <c r="D36">
         <v>2022</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" s="1" t="s">
+      <c r="E36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" t="s">
         <v>10</v>
       </c>
       <c r="G36">
@@ -7943,19 +7868,19 @@
       <c r="A37">
         <v>1</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" s="2">
+      <c r="B37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="1">
         <v>44593</v>
       </c>
       <c r="D37">
         <v>2022</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" s="1" t="s">
+      <c r="E37" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" t="s">
         <v>11</v>
       </c>
       <c r="G37">
@@ -7969,19 +7894,19 @@
       <c r="A38">
         <v>1</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="2">
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="1">
         <v>44593</v>
       </c>
       <c r="D38">
         <v>2022</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" s="1" t="s">
+      <c r="E38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" t="s">
         <v>12</v>
       </c>
       <c r="G38">
@@ -7995,19 +7920,19 @@
       <c r="A39">
         <v>1</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C39" s="2">
+      <c r="B39" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="1">
         <v>44621</v>
       </c>
       <c r="D39">
         <v>2022</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" s="1" t="s">
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" t="s">
         <v>10</v>
       </c>
       <c r="G39">
@@ -8021,19 +7946,19 @@
       <c r="A40">
         <v>1</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C40" s="2">
+      <c r="B40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="1">
         <v>44621</v>
       </c>
       <c r="D40">
         <v>2022</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" s="1" t="s">
+      <c r="E40" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" t="s">
         <v>11</v>
       </c>
       <c r="G40">
@@ -8047,19 +7972,19 @@
       <c r="A41">
         <v>1</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C41" s="2">
+      <c r="B41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="1">
         <v>44621</v>
       </c>
       <c r="D41">
         <v>2022</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" s="1" t="s">
+      <c r="E41" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" t="s">
         <v>12</v>
       </c>
       <c r="G41">
@@ -8073,19 +7998,19 @@
       <c r="A42">
         <v>1</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" s="2">
+      <c r="B42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="1">
         <v>44652</v>
       </c>
       <c r="D42">
         <v>2022</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" s="1" t="s">
+      <c r="E42" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" t="s">
         <v>10</v>
       </c>
       <c r="G42">
@@ -8099,19 +8024,19 @@
       <c r="A43">
         <v>1</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C43" s="2">
+      <c r="B43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="1">
         <v>44652</v>
       </c>
       <c r="D43">
         <v>2022</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" s="1" t="s">
+      <c r="E43" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" t="s">
         <v>11</v>
       </c>
       <c r="G43">
@@ -8125,19 +8050,19 @@
       <c r="A44">
         <v>1</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C44" s="2">
+      <c r="B44" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="1">
         <v>44652</v>
       </c>
       <c r="D44">
         <v>2022</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" s="1" t="s">
+      <c r="E44" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" t="s">
         <v>12</v>
       </c>
       <c r="G44">
@@ -8151,19 +8076,19 @@
       <c r="A45">
         <v>1</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45" s="2">
+      <c r="B45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="1">
         <v>44682</v>
       </c>
       <c r="D45">
         <v>2022</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" s="1" t="s">
+      <c r="E45" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45" t="s">
         <v>10</v>
       </c>
       <c r="G45">
@@ -8177,19 +8102,19 @@
       <c r="A46">
         <v>1</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C46" s="2">
+      <c r="B46" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="1">
         <v>44682</v>
       </c>
       <c r="D46">
         <v>2022</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" s="1" t="s">
+      <c r="E46" t="s">
+        <v>9</v>
+      </c>
+      <c r="F46" t="s">
         <v>11</v>
       </c>
       <c r="G46">
@@ -8203,19 +8128,19 @@
       <c r="A47">
         <v>1</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C47" s="2">
+      <c r="B47" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="1">
         <v>44682</v>
       </c>
       <c r="D47">
         <v>2022</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" s="1" t="s">
+      <c r="E47" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" t="s">
         <v>12</v>
       </c>
       <c r="G47">
@@ -8229,19 +8154,19 @@
       <c r="A48">
         <v>1</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" s="2">
+      <c r="B48" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="1">
         <v>44713</v>
       </c>
       <c r="D48">
         <v>2022</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F48" s="1" t="s">
+      <c r="E48" t="s">
+        <v>9</v>
+      </c>
+      <c r="F48" t="s">
         <v>10</v>
       </c>
       <c r="G48">
@@ -8255,19 +8180,19 @@
       <c r="A49">
         <v>1</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C49" s="2">
+      <c r="B49" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="1">
         <v>44713</v>
       </c>
       <c r="D49">
         <v>2022</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" s="1" t="s">
+      <c r="E49" t="s">
+        <v>9</v>
+      </c>
+      <c r="F49" t="s">
         <v>11</v>
       </c>
       <c r="G49">
@@ -8281,19 +8206,19 @@
       <c r="A50">
         <v>1</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C50" s="2">
+      <c r="B50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="1">
         <v>44713</v>
       </c>
       <c r="D50">
         <v>2022</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" s="1" t="s">
+      <c r="E50" t="s">
+        <v>9</v>
+      </c>
+      <c r="F50" t="s">
         <v>12</v>
       </c>
       <c r="G50">
@@ -8307,19 +8232,19 @@
       <c r="A51">
         <v>1</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C51" s="2">
+      <c r="B51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="1">
         <v>44743</v>
       </c>
       <c r="D51">
         <v>2022</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" s="1" t="s">
+      <c r="E51" t="s">
+        <v>9</v>
+      </c>
+      <c r="F51" t="s">
         <v>10</v>
       </c>
       <c r="G51">
@@ -8333,19 +8258,19 @@
       <c r="A52">
         <v>1</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C52" s="2">
+      <c r="B52" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="1">
         <v>44743</v>
       </c>
       <c r="D52">
         <v>2022</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F52" s="1" t="s">
+      <c r="E52" t="s">
+        <v>9</v>
+      </c>
+      <c r="F52" t="s">
         <v>11</v>
       </c>
       <c r="G52">
@@ -8359,19 +8284,19 @@
       <c r="A53">
         <v>1</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C53" s="2">
+      <c r="B53" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="1">
         <v>44743</v>
       </c>
       <c r="D53">
         <v>2022</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F53" s="1" t="s">
+      <c r="E53" t="s">
+        <v>9</v>
+      </c>
+      <c r="F53" t="s">
         <v>12</v>
       </c>
       <c r="G53">
@@ -8385,19 +8310,19 @@
       <c r="A54">
         <v>1</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C54" s="2">
+      <c r="B54" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="1">
         <v>44774</v>
       </c>
       <c r="D54">
         <v>2022</v>
       </c>
-      <c r="E54" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F54" s="1" t="s">
+      <c r="E54" t="s">
+        <v>9</v>
+      </c>
+      <c r="F54" t="s">
         <v>10</v>
       </c>
       <c r="G54">
@@ -8411,19 +8336,19 @@
       <c r="A55">
         <v>1</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C55" s="2">
+      <c r="B55" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" s="1">
         <v>44774</v>
       </c>
       <c r="D55">
         <v>2022</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F55" s="1" t="s">
+      <c r="E55" t="s">
+        <v>9</v>
+      </c>
+      <c r="F55" t="s">
         <v>11</v>
       </c>
       <c r="G55">
@@ -8437,19 +8362,19 @@
       <c r="A56">
         <v>1</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C56" s="2">
+      <c r="B56" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="1">
         <v>44805</v>
       </c>
       <c r="D56">
         <v>2022</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F56" s="1" t="s">
+      <c r="E56" t="s">
+        <v>9</v>
+      </c>
+      <c r="F56" t="s">
         <v>10</v>
       </c>
       <c r="G56">
@@ -8463,19 +8388,19 @@
       <c r="A57">
         <v>1</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C57" s="2">
+      <c r="B57" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" s="1">
         <v>44805</v>
       </c>
       <c r="D57">
         <v>2022</v>
       </c>
-      <c r="E57" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F57" s="1" t="s">
+      <c r="E57" t="s">
+        <v>9</v>
+      </c>
+      <c r="F57" t="s">
         <v>11</v>
       </c>
       <c r="G57">
@@ -8489,19 +8414,19 @@
       <c r="A58">
         <v>1</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C58" s="2">
+      <c r="B58" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58" s="1">
         <v>44866</v>
       </c>
       <c r="D58">
         <v>2022</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F58" s="1" t="s">
+      <c r="E58" t="s">
+        <v>9</v>
+      </c>
+      <c r="F58" t="s">
         <v>10</v>
       </c>
       <c r="G58">
@@ -8515,19 +8440,19 @@
       <c r="A59">
         <v>1</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C59" s="2">
+      <c r="B59" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" s="1">
         <v>44866</v>
       </c>
       <c r="D59">
         <v>2022</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" s="1" t="s">
+      <c r="E59" t="s">
+        <v>9</v>
+      </c>
+      <c r="F59" t="s">
         <v>11</v>
       </c>
       <c r="G59">
@@ -8541,19 +8466,19 @@
       <c r="A60">
         <v>1</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C60" s="2">
+      <c r="B60" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60" s="1">
         <v>44866</v>
       </c>
       <c r="D60">
         <v>2022</v>
       </c>
-      <c r="E60" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F60" s="1" t="s">
+      <c r="E60" t="s">
+        <v>9</v>
+      </c>
+      <c r="F60" t="s">
         <v>12</v>
       </c>
       <c r="G60">
@@ -8567,19 +8492,19 @@
       <c r="A61">
         <v>1</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C61" s="2">
+      <c r="B61" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61" s="1">
         <v>44896</v>
       </c>
       <c r="D61">
         <v>2022</v>
       </c>
-      <c r="E61" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F61" s="1" t="s">
+      <c r="E61" t="s">
+        <v>9</v>
+      </c>
+      <c r="F61" t="s">
         <v>10</v>
       </c>
       <c r="G61">
@@ -8593,19 +8518,19 @@
       <c r="A62">
         <v>1</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C62" s="2">
+      <c r="B62" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62" s="1">
         <v>44896</v>
       </c>
       <c r="D62">
         <v>2022</v>
       </c>
-      <c r="E62" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F62" s="1" t="s">
+      <c r="E62" t="s">
+        <v>9</v>
+      </c>
+      <c r="F62" t="s">
         <v>11</v>
       </c>
       <c r="G62">
@@ -8619,19 +8544,19 @@
       <c r="A63">
         <v>1</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C63" s="2">
+      <c r="B63" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" s="1">
         <v>44896</v>
       </c>
       <c r="D63">
         <v>2022</v>
       </c>
-      <c r="E63" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F63" s="1" t="s">
+      <c r="E63" t="s">
+        <v>9</v>
+      </c>
+      <c r="F63" t="s">
         <v>12</v>
       </c>
       <c r="G63">
@@ -8645,19 +8570,19 @@
       <c r="A64">
         <v>1</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C64" s="2">
+      <c r="B64" t="s">
+        <v>8</v>
+      </c>
+      <c r="C64" s="1">
         <v>44958</v>
       </c>
       <c r="D64">
         <v>2023</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64" s="1" t="s">
+      <c r="E64" t="s">
+        <v>9</v>
+      </c>
+      <c r="F64" t="s">
         <v>11</v>
       </c>
       <c r="G64">
@@ -8671,19 +8596,19 @@
       <c r="A65">
         <v>1</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C65" s="2">
+      <c r="B65" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65" s="1">
         <v>44986</v>
       </c>
       <c r="D65">
         <v>2023</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F65" s="1" t="s">
+      <c r="E65" t="s">
+        <v>9</v>
+      </c>
+      <c r="F65" t="s">
         <v>10</v>
       </c>
       <c r="G65">
@@ -8697,19 +8622,19 @@
       <c r="A66">
         <v>1</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C66" s="2">
+      <c r="B66" t="s">
+        <v>8</v>
+      </c>
+      <c r="C66" s="1">
         <v>44986</v>
       </c>
       <c r="D66">
         <v>2023</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F66" s="1" t="s">
+      <c r="E66" t="s">
+        <v>9</v>
+      </c>
+      <c r="F66" t="s">
         <v>11</v>
       </c>
       <c r="G66">
@@ -8723,19 +8648,19 @@
       <c r="A67">
         <v>1</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C67" s="2">
+      <c r="B67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67" s="1">
         <v>44986</v>
       </c>
       <c r="D67">
         <v>2023</v>
       </c>
-      <c r="E67" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F67" s="1" t="s">
+      <c r="E67" t="s">
+        <v>9</v>
+      </c>
+      <c r="F67" t="s">
         <v>12</v>
       </c>
       <c r="G67">
@@ -8749,19 +8674,19 @@
       <c r="A68">
         <v>1</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C68" s="2">
+      <c r="B68" t="s">
+        <v>8</v>
+      </c>
+      <c r="C68" s="1">
         <v>45017</v>
       </c>
       <c r="D68">
         <v>2023</v>
       </c>
-      <c r="E68" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F68" s="1" t="s">
+      <c r="E68" t="s">
+        <v>9</v>
+      </c>
+      <c r="F68" t="s">
         <v>10</v>
       </c>
       <c r="G68">
@@ -8775,19 +8700,19 @@
       <c r="A69">
         <v>1</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C69" s="2">
+      <c r="B69" t="s">
+        <v>8</v>
+      </c>
+      <c r="C69" s="1">
         <v>45017</v>
       </c>
       <c r="D69">
         <v>2023</v>
       </c>
-      <c r="E69" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F69" s="1" t="s">
+      <c r="E69" t="s">
+        <v>9</v>
+      </c>
+      <c r="F69" t="s">
         <v>11</v>
       </c>
       <c r="G69">
@@ -8801,19 +8726,19 @@
       <c r="A70">
         <v>1</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C70" s="2">
+      <c r="B70" t="s">
+        <v>8</v>
+      </c>
+      <c r="C70" s="1">
         <v>45017</v>
       </c>
       <c r="D70">
         <v>2023</v>
       </c>
-      <c r="E70" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F70" s="1" t="s">
+      <c r="E70" t="s">
+        <v>9</v>
+      </c>
+      <c r="F70" t="s">
         <v>12</v>
       </c>
       <c r="G70">
@@ -8827,19 +8752,19 @@
       <c r="A71">
         <v>1</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C71" s="2">
+      <c r="B71" t="s">
+        <v>8</v>
+      </c>
+      <c r="C71" s="1">
         <v>45047</v>
       </c>
       <c r="D71">
         <v>2023</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F71" s="1" t="s">
+      <c r="E71" t="s">
+        <v>9</v>
+      </c>
+      <c r="F71" t="s">
         <v>11</v>
       </c>
       <c r="G71">
@@ -8853,19 +8778,19 @@
       <c r="A72">
         <v>1</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C72" s="2">
+      <c r="B72" t="s">
+        <v>8</v>
+      </c>
+      <c r="C72" s="1">
         <v>45047</v>
       </c>
       <c r="D72">
         <v>2023</v>
       </c>
-      <c r="E72" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F72" s="1" t="s">
+      <c r="E72" t="s">
+        <v>9</v>
+      </c>
+      <c r="F72" t="s">
         <v>12</v>
       </c>
       <c r="G72">
@@ -8879,19 +8804,19 @@
       <c r="A73">
         <v>1</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C73" s="2">
+      <c r="B73" t="s">
+        <v>8</v>
+      </c>
+      <c r="C73" s="1">
         <v>45078</v>
       </c>
       <c r="D73">
         <v>2023</v>
       </c>
-      <c r="E73" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F73" s="1" t="s">
+      <c r="E73" t="s">
+        <v>9</v>
+      </c>
+      <c r="F73" t="s">
         <v>11</v>
       </c>
       <c r="G73">
@@ -8905,19 +8830,19 @@
       <c r="A74">
         <v>1</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C74" s="2">
+      <c r="B74" t="s">
+        <v>8</v>
+      </c>
+      <c r="C74" s="1">
         <v>45078</v>
       </c>
       <c r="D74">
         <v>2023</v>
       </c>
-      <c r="E74" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" s="1" t="s">
+      <c r="E74" t="s">
+        <v>9</v>
+      </c>
+      <c r="F74" t="s">
         <v>12</v>
       </c>
       <c r="G74">
@@ -8931,19 +8856,19 @@
       <c r="A75">
         <v>1</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C75" s="2">
+      <c r="B75" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75" s="1">
         <v>45108</v>
       </c>
       <c r="D75">
         <v>2023</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F75" s="1" t="s">
+      <c r="E75" t="s">
+        <v>9</v>
+      </c>
+      <c r="F75" t="s">
         <v>10</v>
       </c>
       <c r="G75">
@@ -8957,19 +8882,19 @@
       <c r="A76">
         <v>1</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C76" s="2">
+      <c r="B76" t="s">
+        <v>8</v>
+      </c>
+      <c r="C76" s="1">
         <v>45108</v>
       </c>
       <c r="D76">
         <v>2023</v>
       </c>
-      <c r="E76" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F76" s="1" t="s">
+      <c r="E76" t="s">
+        <v>9</v>
+      </c>
+      <c r="F76" t="s">
         <v>11</v>
       </c>
       <c r="G76">
@@ -8983,19 +8908,19 @@
       <c r="A77">
         <v>1</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C77" s="2">
+      <c r="B77" t="s">
+        <v>8</v>
+      </c>
+      <c r="C77" s="1">
         <v>45108</v>
       </c>
       <c r="D77">
         <v>2023</v>
       </c>
-      <c r="E77" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F77" s="1" t="s">
+      <c r="E77" t="s">
+        <v>9</v>
+      </c>
+      <c r="F77" t="s">
         <v>12</v>
       </c>
       <c r="G77">
@@ -9009,19 +8934,19 @@
       <c r="A78">
         <v>1</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C78" s="2">
+      <c r="B78" t="s">
+        <v>8</v>
+      </c>
+      <c r="C78" s="1">
         <v>45139</v>
       </c>
       <c r="D78">
         <v>2023</v>
       </c>
-      <c r="E78" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F78" s="1" t="s">
+      <c r="E78" t="s">
+        <v>9</v>
+      </c>
+      <c r="F78" t="s">
         <v>10</v>
       </c>
       <c r="G78">
@@ -9035,19 +8960,19 @@
       <c r="A79">
         <v>1</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C79" s="2">
+      <c r="B79" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79" s="1">
         <v>45139</v>
       </c>
       <c r="D79">
         <v>2023</v>
       </c>
-      <c r="E79" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F79" s="1" t="s">
+      <c r="E79" t="s">
+        <v>9</v>
+      </c>
+      <c r="F79" t="s">
         <v>11</v>
       </c>
       <c r="G79">
@@ -9061,19 +8986,19 @@
       <c r="A80">
         <v>1</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C80" s="2">
+      <c r="B80" t="s">
+        <v>8</v>
+      </c>
+      <c r="C80" s="1">
         <v>45139</v>
       </c>
       <c r="D80">
         <v>2023</v>
       </c>
-      <c r="E80" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F80" s="1" t="s">
+      <c r="E80" t="s">
+        <v>9</v>
+      </c>
+      <c r="F80" t="s">
         <v>12</v>
       </c>
       <c r="G80">
@@ -9087,19 +9012,19 @@
       <c r="A81">
         <v>1</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C81" s="2">
+      <c r="B81" t="s">
+        <v>8</v>
+      </c>
+      <c r="C81" s="1">
         <v>45170</v>
       </c>
       <c r="D81">
         <v>2023</v>
       </c>
-      <c r="E81" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F81" s="1" t="s">
+      <c r="E81" t="s">
+        <v>9</v>
+      </c>
+      <c r="F81" t="s">
         <v>10</v>
       </c>
       <c r="G81">
@@ -9113,19 +9038,19 @@
       <c r="A82">
         <v>1</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C82" s="2">
+      <c r="B82" t="s">
+        <v>8</v>
+      </c>
+      <c r="C82" s="1">
         <v>45170</v>
       </c>
       <c r="D82">
         <v>2023</v>
       </c>
-      <c r="E82" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F82" s="1" t="s">
+      <c r="E82" t="s">
+        <v>9</v>
+      </c>
+      <c r="F82" t="s">
         <v>11</v>
       </c>
       <c r="G82">
@@ -9139,19 +9064,19 @@
       <c r="A83">
         <v>1</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C83" s="2">
+      <c r="B83" t="s">
+        <v>8</v>
+      </c>
+      <c r="C83" s="1">
         <v>45170</v>
       </c>
       <c r="D83">
         <v>2023</v>
       </c>
-      <c r="E83" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F83" s="1" t="s">
+      <c r="E83" t="s">
+        <v>9</v>
+      </c>
+      <c r="F83" t="s">
         <v>12</v>
       </c>
       <c r="G83">
@@ -9165,19 +9090,19 @@
       <c r="A84">
         <v>1</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C84" s="2">
+      <c r="B84" t="s">
+        <v>8</v>
+      </c>
+      <c r="C84" s="1">
         <v>45200</v>
       </c>
       <c r="D84">
         <v>2023</v>
       </c>
-      <c r="E84" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F84" s="1" t="s">
+      <c r="E84" t="s">
+        <v>9</v>
+      </c>
+      <c r="F84" t="s">
         <v>10</v>
       </c>
       <c r="G84">
@@ -9191,19 +9116,19 @@
       <c r="A85">
         <v>1</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C85" s="2">
+      <c r="B85" t="s">
+        <v>8</v>
+      </c>
+      <c r="C85" s="1">
         <v>45200</v>
       </c>
       <c r="D85">
         <v>2023</v>
       </c>
-      <c r="E85" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F85" s="1" t="s">
+      <c r="E85" t="s">
+        <v>9</v>
+      </c>
+      <c r="F85" t="s">
         <v>11</v>
       </c>
       <c r="G85">
@@ -9217,19 +9142,19 @@
       <c r="A86">
         <v>1</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C86" s="2">
+      <c r="B86" t="s">
+        <v>8</v>
+      </c>
+      <c r="C86" s="1">
         <v>45200</v>
       </c>
       <c r="D86">
         <v>2023</v>
       </c>
-      <c r="E86" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F86" s="1" t="s">
+      <c r="E86" t="s">
+        <v>9</v>
+      </c>
+      <c r="F86" t="s">
         <v>12</v>
       </c>
       <c r="G86">
@@ -9243,19 +9168,19 @@
       <c r="A87">
         <v>1</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C87" s="2">
+      <c r="B87" t="s">
+        <v>8</v>
+      </c>
+      <c r="C87" s="1">
         <v>45231</v>
       </c>
       <c r="D87">
         <v>2023</v>
       </c>
-      <c r="E87" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F87" s="1" t="s">
+      <c r="E87" t="s">
+        <v>9</v>
+      </c>
+      <c r="F87" t="s">
         <v>11</v>
       </c>
       <c r="G87">
@@ -9269,19 +9194,19 @@
       <c r="A88">
         <v>1</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C88" s="2">
+      <c r="B88" t="s">
+        <v>8</v>
+      </c>
+      <c r="C88" s="1">
         <v>45231</v>
       </c>
       <c r="D88">
         <v>2023</v>
       </c>
-      <c r="E88" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F88" s="1" t="s">
+      <c r="E88" t="s">
+        <v>9</v>
+      </c>
+      <c r="F88" t="s">
         <v>12</v>
       </c>
       <c r="G88">
@@ -9295,19 +9220,19 @@
       <c r="A89">
         <v>1</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C89" s="2">
+      <c r="B89" t="s">
+        <v>8</v>
+      </c>
+      <c r="C89" s="1">
         <v>45261</v>
       </c>
       <c r="D89">
         <v>2023</v>
       </c>
-      <c r="E89" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F89" s="1" t="s">
+      <c r="E89" t="s">
+        <v>9</v>
+      </c>
+      <c r="F89" t="s">
         <v>11</v>
       </c>
       <c r="G89">
@@ -9321,19 +9246,19 @@
       <c r="A90">
         <v>1</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C90" s="2">
+      <c r="B90" t="s">
+        <v>8</v>
+      </c>
+      <c r="C90" s="1">
         <v>45261</v>
       </c>
       <c r="D90">
         <v>2023</v>
       </c>
-      <c r="E90" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F90" s="1" t="s">
+      <c r="E90" t="s">
+        <v>9</v>
+      </c>
+      <c r="F90" t="s">
         <v>12</v>
       </c>
       <c r="G90">
@@ -9347,19 +9272,19 @@
       <c r="A91">
         <v>1</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C91" s="2">
+      <c r="B91" t="s">
+        <v>8</v>
+      </c>
+      <c r="C91" s="1">
         <v>45292</v>
       </c>
       <c r="D91">
         <v>2024</v>
       </c>
-      <c r="E91" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F91" s="1" t="s">
+      <c r="E91" t="s">
+        <v>9</v>
+      </c>
+      <c r="F91" t="s">
         <v>11</v>
       </c>
       <c r="G91">
@@ -9373,19 +9298,19 @@
       <c r="A92">
         <v>1</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C92" s="2">
+      <c r="B92" t="s">
+        <v>8</v>
+      </c>
+      <c r="C92" s="1">
         <v>45292</v>
       </c>
       <c r="D92">
         <v>2024</v>
       </c>
-      <c r="E92" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F92" s="1" t="s">
+      <c r="E92" t="s">
+        <v>9</v>
+      </c>
+      <c r="F92" t="s">
         <v>12</v>
       </c>
       <c r="G92">
@@ -9399,19 +9324,19 @@
       <c r="A93">
         <v>1</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C93" s="2">
+      <c r="B93" t="s">
+        <v>8</v>
+      </c>
+      <c r="C93" s="1">
         <v>45323</v>
       </c>
       <c r="D93">
         <v>2024</v>
       </c>
-      <c r="E93" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F93" s="1" t="s">
+      <c r="E93" t="s">
+        <v>9</v>
+      </c>
+      <c r="F93" t="s">
         <v>10</v>
       </c>
       <c r="G93">
@@ -9425,19 +9350,19 @@
       <c r="A94">
         <v>1</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C94" s="2">
+      <c r="B94" t="s">
+        <v>8</v>
+      </c>
+      <c r="C94" s="1">
         <v>45323</v>
       </c>
       <c r="D94">
         <v>2024</v>
       </c>
-      <c r="E94" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F94" s="1" t="s">
+      <c r="E94" t="s">
+        <v>9</v>
+      </c>
+      <c r="F94" t="s">
         <v>11</v>
       </c>
       <c r="G94">
@@ -9451,19 +9376,19 @@
       <c r="A95">
         <v>1</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C95" s="2">
+      <c r="B95" t="s">
+        <v>8</v>
+      </c>
+      <c r="C95" s="1">
         <v>45323</v>
       </c>
       <c r="D95">
         <v>2024</v>
       </c>
-      <c r="E95" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F95" s="1" t="s">
+      <c r="E95" t="s">
+        <v>9</v>
+      </c>
+      <c r="F95" t="s">
         <v>12</v>
       </c>
       <c r="G95">
@@ -9477,19 +9402,19 @@
       <c r="A96">
         <v>1</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C96" s="2">
+      <c r="B96" t="s">
+        <v>8</v>
+      </c>
+      <c r="C96" s="1">
         <v>45352</v>
       </c>
       <c r="D96">
         <v>2024</v>
       </c>
-      <c r="E96" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F96" s="1" t="s">
+      <c r="E96" t="s">
+        <v>9</v>
+      </c>
+      <c r="F96" t="s">
         <v>11</v>
       </c>
       <c r="G96">
@@ -9503,19 +9428,19 @@
       <c r="A97">
         <v>1</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C97" s="2">
+      <c r="B97" t="s">
+        <v>8</v>
+      </c>
+      <c r="C97" s="1">
         <v>45352</v>
       </c>
       <c r="D97">
         <v>2024</v>
       </c>
-      <c r="E97" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F97" s="1" t="s">
+      <c r="E97" t="s">
+        <v>9</v>
+      </c>
+      <c r="F97" t="s">
         <v>12</v>
       </c>
       <c r="G97">
@@ -9529,19 +9454,19 @@
       <c r="A98">
         <v>1</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C98" s="2">
+      <c r="B98" t="s">
+        <v>8</v>
+      </c>
+      <c r="C98" s="1">
         <v>45383</v>
       </c>
       <c r="D98">
         <v>2024</v>
       </c>
-      <c r="E98" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F98" s="1" t="s">
+      <c r="E98" t="s">
+        <v>9</v>
+      </c>
+      <c r="F98" t="s">
         <v>11</v>
       </c>
       <c r="G98">
@@ -9555,19 +9480,19 @@
       <c r="A99">
         <v>1</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C99" s="2">
+      <c r="B99" t="s">
+        <v>8</v>
+      </c>
+      <c r="C99" s="1">
         <v>45383</v>
       </c>
       <c r="D99">
         <v>2024</v>
       </c>
-      <c r="E99" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F99" s="1" t="s">
+      <c r="E99" t="s">
+        <v>9</v>
+      </c>
+      <c r="F99" t="s">
         <v>12</v>
       </c>
       <c r="G99">
@@ -9581,19 +9506,19 @@
       <c r="A100">
         <v>1</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C100" s="2">
+      <c r="B100" t="s">
+        <v>8</v>
+      </c>
+      <c r="C100" s="1">
         <v>45413</v>
       </c>
       <c r="D100">
         <v>2024</v>
       </c>
-      <c r="E100" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F100" s="1" t="s">
+      <c r="E100" t="s">
+        <v>9</v>
+      </c>
+      <c r="F100" t="s">
         <v>10</v>
       </c>
       <c r="G100">
@@ -9607,19 +9532,19 @@
       <c r="A101">
         <v>1</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C101" s="2">
+      <c r="B101" t="s">
+        <v>8</v>
+      </c>
+      <c r="C101" s="1">
         <v>45413</v>
       </c>
       <c r="D101">
         <v>2024</v>
       </c>
-      <c r="E101" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F101" s="1" t="s">
+      <c r="E101" t="s">
+        <v>9</v>
+      </c>
+      <c r="F101" t="s">
         <v>11</v>
       </c>
       <c r="G101">
@@ -9633,19 +9558,19 @@
       <c r="A102">
         <v>1</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C102" s="2">
+      <c r="B102" t="s">
+        <v>8</v>
+      </c>
+      <c r="C102" s="1">
         <v>45413</v>
       </c>
       <c r="D102">
         <v>2024</v>
       </c>
-      <c r="E102" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F102" s="1" t="s">
+      <c r="E102" t="s">
+        <v>9</v>
+      </c>
+      <c r="F102" t="s">
         <v>12</v>
       </c>
       <c r="G102">
@@ -9659,19 +9584,19 @@
       <c r="A103">
         <v>1</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C103" s="2">
+      <c r="B103" t="s">
+        <v>8</v>
+      </c>
+      <c r="C103" s="1">
         <v>45444</v>
       </c>
       <c r="D103">
         <v>2024</v>
       </c>
-      <c r="E103" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F103" s="1" t="s">
+      <c r="E103" t="s">
+        <v>9</v>
+      </c>
+      <c r="F103" t="s">
         <v>10</v>
       </c>
       <c r="G103">
@@ -9685,19 +9610,19 @@
       <c r="A104">
         <v>1</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C104" s="2">
+      <c r="B104" t="s">
+        <v>8</v>
+      </c>
+      <c r="C104" s="1">
         <v>45444</v>
       </c>
       <c r="D104">
         <v>2024</v>
       </c>
-      <c r="E104" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F104" s="1" t="s">
+      <c r="E104" t="s">
+        <v>9</v>
+      </c>
+      <c r="F104" t="s">
         <v>11</v>
       </c>
       <c r="G104">
@@ -9711,19 +9636,19 @@
       <c r="A105">
         <v>1</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C105" s="2">
+      <c r="B105" t="s">
+        <v>8</v>
+      </c>
+      <c r="C105" s="1">
         <v>45444</v>
       </c>
       <c r="D105">
         <v>2024</v>
       </c>
-      <c r="E105" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F105" s="1" t="s">
+      <c r="E105" t="s">
+        <v>9</v>
+      </c>
+      <c r="F105" t="s">
         <v>12</v>
       </c>
       <c r="G105">
@@ -9737,19 +9662,19 @@
       <c r="A106">
         <v>1</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C106" s="2">
+      <c r="B106" t="s">
+        <v>8</v>
+      </c>
+      <c r="C106" s="1">
         <v>45474</v>
       </c>
       <c r="D106">
         <v>2024</v>
       </c>
-      <c r="E106" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F106" s="1" t="s">
+      <c r="E106" t="s">
+        <v>9</v>
+      </c>
+      <c r="F106" t="s">
         <v>11</v>
       </c>
       <c r="G106">
@@ -9763,19 +9688,19 @@
       <c r="A107">
         <v>1</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C107" s="2">
+      <c r="B107" t="s">
+        <v>8</v>
+      </c>
+      <c r="C107" s="1">
         <v>45474</v>
       </c>
       <c r="D107">
         <v>2024</v>
       </c>
-      <c r="E107" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F107" s="1" t="s">
+      <c r="E107" t="s">
+        <v>9</v>
+      </c>
+      <c r="F107" t="s">
         <v>12</v>
       </c>
       <c r="G107">
@@ -9789,19 +9714,19 @@
       <c r="A108">
         <v>1</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C108" s="2">
+      <c r="B108" t="s">
+        <v>8</v>
+      </c>
+      <c r="C108" s="1">
         <v>45505</v>
       </c>
       <c r="D108">
         <v>2024</v>
       </c>
-      <c r="E108" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F108" s="1" t="s">
+      <c r="E108" t="s">
+        <v>9</v>
+      </c>
+      <c r="F108" t="s">
         <v>10</v>
       </c>
       <c r="G108">
@@ -9815,19 +9740,19 @@
       <c r="A109">
         <v>1</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C109" s="2">
+      <c r="B109" t="s">
+        <v>8</v>
+      </c>
+      <c r="C109" s="1">
         <v>45505</v>
       </c>
       <c r="D109">
         <v>2024</v>
       </c>
-      <c r="E109" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F109" s="1" t="s">
+      <c r="E109" t="s">
+        <v>9</v>
+      </c>
+      <c r="F109" t="s">
         <v>11</v>
       </c>
       <c r="G109">
@@ -9841,19 +9766,19 @@
       <c r="A110">
         <v>1</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C110" s="2">
+      <c r="B110" t="s">
+        <v>8</v>
+      </c>
+      <c r="C110" s="1">
         <v>45505</v>
       </c>
       <c r="D110">
         <v>2024</v>
       </c>
-      <c r="E110" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F110" s="1" t="s">
+      <c r="E110" t="s">
+        <v>9</v>
+      </c>
+      <c r="F110" t="s">
         <v>12</v>
       </c>
       <c r="G110">
@@ -9867,19 +9792,19 @@
       <c r="A111">
         <v>1</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C111" s="2">
+      <c r="B111" t="s">
+        <v>8</v>
+      </c>
+      <c r="C111" s="1">
         <v>45536</v>
       </c>
       <c r="D111">
         <v>2024</v>
       </c>
-      <c r="E111" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F111" s="1" t="s">
+      <c r="E111" t="s">
+        <v>9</v>
+      </c>
+      <c r="F111" t="s">
         <v>11</v>
       </c>
       <c r="G111">
@@ -9893,19 +9818,19 @@
       <c r="A112">
         <v>1</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C112" s="2">
+      <c r="B112" t="s">
+        <v>8</v>
+      </c>
+      <c r="C112" s="1">
         <v>45536</v>
       </c>
       <c r="D112">
         <v>2024</v>
       </c>
-      <c r="E112" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F112" s="1" t="s">
+      <c r="E112" t="s">
+        <v>9</v>
+      </c>
+      <c r="F112" t="s">
         <v>12</v>
       </c>
       <c r="G112">
@@ -9919,19 +9844,19 @@
       <c r="A113">
         <v>1</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C113" s="2">
+      <c r="B113" t="s">
+        <v>8</v>
+      </c>
+      <c r="C113" s="1">
         <v>45566</v>
       </c>
       <c r="D113">
         <v>2024</v>
       </c>
-      <c r="E113" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F113" s="1" t="s">
+      <c r="E113" t="s">
+        <v>9</v>
+      </c>
+      <c r="F113" t="s">
         <v>10</v>
       </c>
       <c r="G113">
@@ -9945,19 +9870,19 @@
       <c r="A114">
         <v>1</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C114" s="2">
+      <c r="B114" t="s">
+        <v>8</v>
+      </c>
+      <c r="C114" s="1">
         <v>45566</v>
       </c>
       <c r="D114">
         <v>2024</v>
       </c>
-      <c r="E114" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F114" s="1" t="s">
+      <c r="E114" t="s">
+        <v>9</v>
+      </c>
+      <c r="F114" t="s">
         <v>11</v>
       </c>
       <c r="G114">
@@ -9971,19 +9896,19 @@
       <c r="A115">
         <v>1</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C115" s="2">
+      <c r="B115" t="s">
+        <v>8</v>
+      </c>
+      <c r="C115" s="1">
         <v>45566</v>
       </c>
       <c r="D115">
         <v>2024</v>
       </c>
-      <c r="E115" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F115" s="1" t="s">
+      <c r="E115" t="s">
+        <v>9</v>
+      </c>
+      <c r="F115" t="s">
         <v>12</v>
       </c>
       <c r="G115">
@@ -9997,19 +9922,19 @@
       <c r="A116">
         <v>1</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C116" s="2">
+      <c r="B116" t="s">
+        <v>8</v>
+      </c>
+      <c r="C116" s="1">
         <v>45597</v>
       </c>
       <c r="D116">
         <v>2024</v>
       </c>
-      <c r="E116" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F116" s="1" t="s">
+      <c r="E116" t="s">
+        <v>9</v>
+      </c>
+      <c r="F116" t="s">
         <v>11</v>
       </c>
       <c r="G116">
@@ -10023,19 +9948,19 @@
       <c r="A117">
         <v>1</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C117" s="2">
+      <c r="B117" t="s">
+        <v>8</v>
+      </c>
+      <c r="C117" s="1">
         <v>45597</v>
       </c>
       <c r="D117">
         <v>2024</v>
       </c>
-      <c r="E117" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F117" s="1" t="s">
+      <c r="E117" t="s">
+        <v>9</v>
+      </c>
+      <c r="F117" t="s">
         <v>12</v>
       </c>
       <c r="G117">
@@ -10049,19 +9974,19 @@
       <c r="A118">
         <v>1</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C118" s="2">
+      <c r="B118" t="s">
+        <v>8</v>
+      </c>
+      <c r="C118" s="1">
         <v>45627</v>
       </c>
       <c r="D118">
         <v>2024</v>
       </c>
-      <c r="E118" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F118" s="1" t="s">
+      <c r="E118" t="s">
+        <v>9</v>
+      </c>
+      <c r="F118" t="s">
         <v>10</v>
       </c>
       <c r="G118">
@@ -10075,19 +10000,19 @@
       <c r="A119">
         <v>1</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C119" s="2">
+      <c r="B119" t="s">
+        <v>8</v>
+      </c>
+      <c r="C119" s="1">
         <v>45627</v>
       </c>
       <c r="D119">
         <v>2024</v>
       </c>
-      <c r="E119" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F119" s="1" t="s">
+      <c r="E119" t="s">
+        <v>9</v>
+      </c>
+      <c r="F119" t="s">
         <v>11</v>
       </c>
       <c r="G119">
@@ -10101,19 +10026,19 @@
       <c r="A120">
         <v>1</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C120" s="2">
+      <c r="B120" t="s">
+        <v>8</v>
+      </c>
+      <c r="C120" s="1">
         <v>45627</v>
       </c>
       <c r="D120">
         <v>2024</v>
       </c>
-      <c r="E120" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F120" s="1" t="s">
+      <c r="E120" t="s">
+        <v>9</v>
+      </c>
+      <c r="F120" t="s">
         <v>12</v>
       </c>
       <c r="G120">
@@ -10127,19 +10052,19 @@
       <c r="A121">
         <v>1</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C121" s="2">
+      <c r="B121" t="s">
+        <v>8</v>
+      </c>
+      <c r="C121" s="1">
         <v>45658</v>
       </c>
       <c r="D121">
         <v>2025</v>
       </c>
-      <c r="E121" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F121" s="1" t="s">
+      <c r="E121" t="s">
+        <v>9</v>
+      </c>
+      <c r="F121" t="s">
         <v>11</v>
       </c>
       <c r="G121">
@@ -10153,19 +10078,19 @@
       <c r="A122">
         <v>1</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C122" s="2">
+      <c r="B122" t="s">
+        <v>8</v>
+      </c>
+      <c r="C122" s="1">
         <v>45658</v>
       </c>
       <c r="D122">
         <v>2025</v>
       </c>
-      <c r="E122" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F122" s="1" t="s">
+      <c r="E122" t="s">
+        <v>9</v>
+      </c>
+      <c r="F122" t="s">
         <v>12</v>
       </c>
       <c r="G122">
@@ -10179,19 +10104,19 @@
       <c r="A123">
         <v>1</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C123" s="2">
+      <c r="B123" t="s">
+        <v>8</v>
+      </c>
+      <c r="C123" s="1">
         <v>45689</v>
       </c>
       <c r="D123">
         <v>2025</v>
       </c>
-      <c r="E123" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F123" s="1" t="s">
+      <c r="E123" t="s">
+        <v>9</v>
+      </c>
+      <c r="F123" t="s">
         <v>11</v>
       </c>
       <c r="G123">
@@ -10205,19 +10130,19 @@
       <c r="A124">
         <v>1</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C124" s="2">
+      <c r="B124" t="s">
+        <v>8</v>
+      </c>
+      <c r="C124" s="1">
         <v>45689</v>
       </c>
       <c r="D124">
         <v>2025</v>
       </c>
-      <c r="E124" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F124" s="1" t="s">
+      <c r="E124" t="s">
+        <v>9</v>
+      </c>
+      <c r="F124" t="s">
         <v>12</v>
       </c>
       <c r="G124">
@@ -10231,19 +10156,19 @@
       <c r="A125">
         <v>1</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C125" s="2">
+      <c r="B125" t="s">
+        <v>8</v>
+      </c>
+      <c r="C125" s="1">
         <v>45717</v>
       </c>
       <c r="D125">
         <v>2025</v>
       </c>
-      <c r="E125" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F125" s="1" t="s">
+      <c r="E125" t="s">
+        <v>9</v>
+      </c>
+      <c r="F125" t="s">
         <v>11</v>
       </c>
       <c r="G125">
@@ -10257,19 +10182,19 @@
       <c r="A126">
         <v>1</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C126" s="2">
+      <c r="B126" t="s">
+        <v>8</v>
+      </c>
+      <c r="C126" s="1">
         <v>45717</v>
       </c>
       <c r="D126">
         <v>2025</v>
       </c>
-      <c r="E126" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F126" s="1" t="s">
+      <c r="E126" t="s">
+        <v>9</v>
+      </c>
+      <c r="F126" t="s">
         <v>12</v>
       </c>
       <c r="G126">
@@ -10283,19 +10208,19 @@
       <c r="A127">
         <v>1</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C127" s="2">
+      <c r="B127" t="s">
+        <v>8</v>
+      </c>
+      <c r="C127" s="1">
         <v>45748</v>
       </c>
       <c r="D127">
         <v>2025</v>
       </c>
-      <c r="E127" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F127" s="1" t="s">
+      <c r="E127" t="s">
+        <v>9</v>
+      </c>
+      <c r="F127" t="s">
         <v>11</v>
       </c>
       <c r="G127">
@@ -10309,19 +10234,19 @@
       <c r="A128">
         <v>1</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C128" s="2">
+      <c r="B128" t="s">
+        <v>8</v>
+      </c>
+      <c r="C128" s="1">
         <v>45748</v>
       </c>
       <c r="D128">
         <v>2025</v>
       </c>
-      <c r="E128" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F128" s="1" t="s">
+      <c r="E128" t="s">
+        <v>9</v>
+      </c>
+      <c r="F128" t="s">
         <v>12</v>
       </c>
       <c r="G128">
@@ -10335,19 +10260,19 @@
       <c r="A129">
         <v>1</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C129" s="2">
+      <c r="B129" t="s">
+        <v>8</v>
+      </c>
+      <c r="C129" s="1">
         <v>45778</v>
       </c>
       <c r="D129">
         <v>2025</v>
       </c>
-      <c r="E129" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F129" s="1" t="s">
+      <c r="E129" t="s">
+        <v>9</v>
+      </c>
+      <c r="F129" t="s">
         <v>10</v>
       </c>
       <c r="G129">
@@ -10361,19 +10286,19 @@
       <c r="A130">
         <v>1</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C130" s="2">
+      <c r="B130" t="s">
+        <v>8</v>
+      </c>
+      <c r="C130" s="1">
         <v>45778</v>
       </c>
       <c r="D130">
         <v>2025</v>
       </c>
-      <c r="E130" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F130" s="1" t="s">
+      <c r="E130" t="s">
+        <v>9</v>
+      </c>
+      <c r="F130" t="s">
         <v>11</v>
       </c>
       <c r="G130">
@@ -10387,19 +10312,19 @@
       <c r="A131">
         <v>1</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C131" s="2">
+      <c r="B131" t="s">
+        <v>8</v>
+      </c>
+      <c r="C131" s="1">
         <v>45778</v>
       </c>
       <c r="D131">
         <v>2025</v>
       </c>
-      <c r="E131" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F131" s="1" t="s">
+      <c r="E131" t="s">
+        <v>9</v>
+      </c>
+      <c r="F131" t="s">
         <v>12</v>
       </c>
       <c r="G131">
@@ -10413,19 +10338,19 @@
       <c r="A132">
         <v>1</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C132" s="2">
+      <c r="B132" t="s">
+        <v>8</v>
+      </c>
+      <c r="C132" s="1">
         <v>45809</v>
       </c>
       <c r="D132">
         <v>2025</v>
       </c>
-      <c r="E132" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F132" s="1" t="s">
+      <c r="E132" t="s">
+        <v>9</v>
+      </c>
+      <c r="F132" t="s">
         <v>10</v>
       </c>
       <c r="G132">
@@ -10439,19 +10364,19 @@
       <c r="A133">
         <v>1</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C133" s="2">
+      <c r="B133" t="s">
+        <v>8</v>
+      </c>
+      <c r="C133" s="1">
         <v>45809</v>
       </c>
       <c r="D133">
         <v>2025</v>
       </c>
-      <c r="E133" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F133" s="1" t="s">
+      <c r="E133" t="s">
+        <v>9</v>
+      </c>
+      <c r="F133" t="s">
         <v>11</v>
       </c>
       <c r="G133">
@@ -10465,19 +10390,19 @@
       <c r="A134">
         <v>1</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C134" s="2">
+      <c r="B134" t="s">
+        <v>8</v>
+      </c>
+      <c r="C134" s="1">
         <v>45809</v>
       </c>
       <c r="D134">
         <v>2025</v>
       </c>
-      <c r="E134" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F134" s="1" t="s">
+      <c r="E134" t="s">
+        <v>9</v>
+      </c>
+      <c r="F134" t="s">
         <v>12</v>
       </c>
       <c r="G134">
@@ -10491,19 +10416,19 @@
       <c r="A135">
         <v>1</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C135" s="2">
+      <c r="B135" t="s">
+        <v>8</v>
+      </c>
+      <c r="C135" s="1">
         <v>45839</v>
       </c>
       <c r="D135">
         <v>2025</v>
       </c>
-      <c r="E135" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F135" s="1" t="s">
+      <c r="E135" t="s">
+        <v>9</v>
+      </c>
+      <c r="F135" t="s">
         <v>10</v>
       </c>
       <c r="G135">
@@ -10517,19 +10442,19 @@
       <c r="A136">
         <v>1</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C136" s="2">
+      <c r="B136" t="s">
+        <v>8</v>
+      </c>
+      <c r="C136" s="1">
         <v>45839</v>
       </c>
       <c r="D136">
         <v>2025</v>
       </c>
-      <c r="E136" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F136" s="1" t="s">
+      <c r="E136" t="s">
+        <v>9</v>
+      </c>
+      <c r="F136" t="s">
         <v>11</v>
       </c>
       <c r="G136">
@@ -10543,19 +10468,19 @@
       <c r="A137">
         <v>1</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C137" s="2">
+      <c r="B137" t="s">
+        <v>8</v>
+      </c>
+      <c r="C137" s="1">
         <v>45839</v>
       </c>
       <c r="D137">
         <v>2025</v>
       </c>
-      <c r="E137" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F137" s="1" t="s">
+      <c r="E137" t="s">
+        <v>9</v>
+      </c>
+      <c r="F137" t="s">
         <v>12</v>
       </c>
       <c r="G137">
@@ -10569,19 +10494,19 @@
       <c r="A138">
         <v>1</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C138" s="2">
+      <c r="B138" t="s">
+        <v>8</v>
+      </c>
+      <c r="C138" s="1">
         <v>45870</v>
       </c>
       <c r="D138">
         <v>2025</v>
       </c>
-      <c r="E138" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F138" s="1" t="s">
+      <c r="E138" t="s">
+        <v>9</v>
+      </c>
+      <c r="F138" t="s">
         <v>11</v>
       </c>
       <c r="G138">
@@ -10595,19 +10520,19 @@
       <c r="A139">
         <v>1</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C139" s="2">
+      <c r="B139" t="s">
+        <v>8</v>
+      </c>
+      <c r="C139" s="1">
         <v>45870</v>
       </c>
       <c r="D139">
         <v>2025</v>
       </c>
-      <c r="E139" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F139" s="1" t="s">
+      <c r="E139" t="s">
+        <v>9</v>
+      </c>
+      <c r="F139" t="s">
         <v>12</v>
       </c>
       <c r="G139">
@@ -10621,19 +10546,19 @@
       <c r="A140">
         <v>1</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C140" s="2">
+      <c r="B140" t="s">
+        <v>8</v>
+      </c>
+      <c r="C140" s="1">
         <v>45901</v>
       </c>
       <c r="D140">
         <v>2025</v>
       </c>
-      <c r="E140" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F140" s="1" t="s">
+      <c r="E140" t="s">
+        <v>9</v>
+      </c>
+      <c r="F140" t="s">
         <v>10</v>
       </c>
       <c r="G140">
@@ -10647,19 +10572,19 @@
       <c r="A141">
         <v>1</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C141" s="2">
+      <c r="B141" t="s">
+        <v>8</v>
+      </c>
+      <c r="C141" s="1">
         <v>45901</v>
       </c>
       <c r="D141">
         <v>2025</v>
       </c>
-      <c r="E141" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F141" s="1" t="s">
+      <c r="E141" t="s">
+        <v>9</v>
+      </c>
+      <c r="F141" t="s">
         <v>11</v>
       </c>
       <c r="G141">
@@ -10673,19 +10598,19 @@
       <c r="A142">
         <v>1</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C142" s="2">
+      <c r="B142" t="s">
+        <v>8</v>
+      </c>
+      <c r="C142" s="1">
         <v>45901</v>
       </c>
       <c r="D142">
         <v>2025</v>
       </c>
-      <c r="E142" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F142" s="1" t="s">
+      <c r="E142" t="s">
+        <v>9</v>
+      </c>
+      <c r="F142" t="s">
         <v>12</v>
       </c>
       <c r="G142">
@@ -10699,19 +10624,19 @@
       <c r="A143">
         <v>1</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C143" s="2">
+      <c r="B143" t="s">
+        <v>8</v>
+      </c>
+      <c r="C143" s="1">
         <v>45931</v>
       </c>
       <c r="D143">
         <v>2025</v>
       </c>
-      <c r="E143" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F143" s="1" t="s">
+      <c r="E143" t="s">
+        <v>9</v>
+      </c>
+      <c r="F143" t="s">
         <v>10</v>
       </c>
       <c r="G143">
@@ -10725,19 +10650,19 @@
       <c r="A144">
         <v>1</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C144" s="2">
+      <c r="B144" t="s">
+        <v>8</v>
+      </c>
+      <c r="C144" s="1">
         <v>45931</v>
       </c>
       <c r="D144">
         <v>2025</v>
       </c>
-      <c r="E144" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F144" s="1" t="s">
+      <c r="E144" t="s">
+        <v>9</v>
+      </c>
+      <c r="F144" t="s">
         <v>11</v>
       </c>
       <c r="G144">
@@ -10751,19 +10676,19 @@
       <c r="A145">
         <v>1</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C145" s="2">
+      <c r="B145" t="s">
+        <v>8</v>
+      </c>
+      <c r="C145" s="1">
         <v>45962</v>
       </c>
       <c r="D145">
         <v>2025</v>
       </c>
-      <c r="E145" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F145" s="1" t="s">
+      <c r="E145" t="s">
+        <v>9</v>
+      </c>
+      <c r="F145" t="s">
         <v>10</v>
       </c>
       <c r="G145">
@@ -10777,19 +10702,19 @@
       <c r="A146">
         <v>1</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C146" s="2">
+      <c r="B146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C146" s="1">
         <v>45962</v>
       </c>
       <c r="D146">
         <v>2025</v>
       </c>
-      <c r="E146" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F146" s="1" t="s">
+      <c r="E146" t="s">
+        <v>9</v>
+      </c>
+      <c r="F146" t="s">
         <v>11</v>
       </c>
       <c r="G146">
@@ -10803,19 +10728,19 @@
       <c r="A147">
         <v>1</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C147" s="2">
+      <c r="B147" t="s">
+        <v>8</v>
+      </c>
+      <c r="C147" s="1">
         <v>45962</v>
       </c>
       <c r="D147">
         <v>2025</v>
       </c>
-      <c r="E147" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F147" s="1" t="s">
+      <c r="E147" t="s">
+        <v>9</v>
+      </c>
+      <c r="F147" t="s">
         <v>12</v>
       </c>
       <c r="G147">
@@ -10829,19 +10754,19 @@
       <c r="A148">
         <v>1</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C148" s="2">
+      <c r="B148" t="s">
+        <v>8</v>
+      </c>
+      <c r="C148" s="1">
         <v>45992</v>
       </c>
       <c r="D148">
         <v>2025</v>
       </c>
-      <c r="E148" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F148" s="1" t="s">
+      <c r="E148" t="s">
+        <v>9</v>
+      </c>
+      <c r="F148" t="s">
         <v>10</v>
       </c>
       <c r="G148">
@@ -10855,19 +10780,19 @@
       <c r="A149">
         <v>1</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C149" s="2">
+      <c r="B149" t="s">
+        <v>8</v>
+      </c>
+      <c r="C149" s="1">
         <v>45992</v>
       </c>
       <c r="D149">
         <v>2025</v>
       </c>
-      <c r="E149" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F149" s="1" t="s">
+      <c r="E149" t="s">
+        <v>9</v>
+      </c>
+      <c r="F149" t="s">
         <v>11</v>
       </c>
       <c r="G149">
@@ -10881,19 +10806,19 @@
       <c r="A150">
         <v>1</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C150" s="2">
+      <c r="B150" t="s">
+        <v>8</v>
+      </c>
+      <c r="C150" s="1">
         <v>45992</v>
       </c>
       <c r="D150">
         <v>2025</v>
       </c>
-      <c r="E150" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F150" s="1" t="s">
+      <c r="E150" t="s">
+        <v>9</v>
+      </c>
+      <c r="F150" t="s">
         <v>12</v>
       </c>
       <c r="G150">
@@ -10907,19 +10832,19 @@
       <c r="A151">
         <v>1</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C151" s="2">
+      <c r="B151" t="s">
+        <v>8</v>
+      </c>
+      <c r="C151" s="1">
         <v>46082</v>
       </c>
       <c r="D151">
         <v>2026</v>
       </c>
-      <c r="E151" s="1" t="s">
+      <c r="E151" t="s">
         <v>13</v>
       </c>
-      <c r="F151" s="1" t="s">
+      <c r="F151" t="s">
         <v>11</v>
       </c>
       <c r="G151">
@@ -10933,19 +10858,19 @@
       <c r="A152">
         <v>1</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C152" s="2">
+      <c r="B152" t="s">
+        <v>8</v>
+      </c>
+      <c r="C152" s="1">
         <v>46082</v>
       </c>
       <c r="D152">
         <v>2026</v>
       </c>
-      <c r="E152" s="1" t="s">
+      <c r="E152" t="s">
         <v>13</v>
       </c>
-      <c r="F152" s="1" t="s">
+      <c r="F152" t="s">
         <v>12</v>
       </c>
       <c r="G152">
@@ -10959,19 +10884,19 @@
       <c r="A153">
         <v>1</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C153" s="2">
+      <c r="B153" t="s">
+        <v>8</v>
+      </c>
+      <c r="C153" s="1">
         <v>46113</v>
       </c>
       <c r="D153">
         <v>2026</v>
       </c>
-      <c r="E153" s="1" t="s">
+      <c r="E153" t="s">
         <v>13</v>
       </c>
-      <c r="F153" s="1" t="s">
+      <c r="F153" t="s">
         <v>10</v>
       </c>
       <c r="G153">
@@ -10985,19 +10910,19 @@
       <c r="A154">
         <v>1</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C154" s="2">
+      <c r="B154" t="s">
+        <v>8</v>
+      </c>
+      <c r="C154" s="1">
         <v>46113</v>
       </c>
       <c r="D154">
         <v>2026</v>
       </c>
-      <c r="E154" s="1" t="s">
+      <c r="E154" t="s">
         <v>13</v>
       </c>
-      <c r="F154" s="1" t="s">
+      <c r="F154" t="s">
         <v>11</v>
       </c>
       <c r="G154">
@@ -11011,19 +10936,19 @@
       <c r="A155">
         <v>1</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C155" s="2">
+      <c r="B155" t="s">
+        <v>8</v>
+      </c>
+      <c r="C155" s="1">
         <v>46113</v>
       </c>
       <c r="D155">
         <v>2026</v>
       </c>
-      <c r="E155" s="1" t="s">
+      <c r="E155" t="s">
         <v>13</v>
       </c>
-      <c r="F155" s="1" t="s">
+      <c r="F155" t="s">
         <v>12</v>
       </c>
       <c r="G155">
@@ -11037,19 +10962,19 @@
       <c r="A156">
         <v>1</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C156" s="2">
+      <c r="B156" t="s">
+        <v>8</v>
+      </c>
+      <c r="C156" s="1">
         <v>46143</v>
       </c>
       <c r="D156">
         <v>2026</v>
       </c>
-      <c r="E156" s="1" t="s">
+      <c r="E156" t="s">
         <v>13</v>
       </c>
-      <c r="F156" s="1" t="s">
+      <c r="F156" t="s">
         <v>10</v>
       </c>
       <c r="G156">
@@ -11063,19 +10988,19 @@
       <c r="A157">
         <v>1</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C157" s="2">
+      <c r="B157" t="s">
+        <v>8</v>
+      </c>
+      <c r="C157" s="1">
         <v>46143</v>
       </c>
       <c r="D157">
         <v>2026</v>
       </c>
-      <c r="E157" s="1" t="s">
+      <c r="E157" t="s">
         <v>13</v>
       </c>
-      <c r="F157" s="1" t="s">
+      <c r="F157" t="s">
         <v>11</v>
       </c>
       <c r="G157">
@@ -11089,19 +11014,19 @@
       <c r="A158">
         <v>1</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C158" s="2">
+      <c r="B158" t="s">
+        <v>8</v>
+      </c>
+      <c r="C158" s="1">
         <v>46143</v>
       </c>
       <c r="D158">
         <v>2026</v>
       </c>
-      <c r="E158" s="1" t="s">
+      <c r="E158" t="s">
         <v>13</v>
       </c>
-      <c r="F158" s="1" t="s">
+      <c r="F158" t="s">
         <v>12</v>
       </c>
       <c r="G158">
@@ -11115,19 +11040,19 @@
       <c r="A159">
         <v>1</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C159" s="2">
+      <c r="B159" t="s">
+        <v>8</v>
+      </c>
+      <c r="C159" s="1">
         <v>46174</v>
       </c>
       <c r="D159">
         <v>2026</v>
       </c>
-      <c r="E159" s="1" t="s">
+      <c r="E159" t="s">
         <v>13</v>
       </c>
-      <c r="F159" s="1" t="s">
+      <c r="F159" t="s">
         <v>10</v>
       </c>
       <c r="G159">
@@ -11141,19 +11066,19 @@
       <c r="A160">
         <v>1</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C160" s="2">
+      <c r="B160" t="s">
+        <v>8</v>
+      </c>
+      <c r="C160" s="1">
         <v>46174</v>
       </c>
       <c r="D160">
         <v>2026</v>
       </c>
-      <c r="E160" s="1" t="s">
+      <c r="E160" t="s">
         <v>13</v>
       </c>
-      <c r="F160" s="1" t="s">
+      <c r="F160" t="s">
         <v>11</v>
       </c>
       <c r="G160">
@@ -11167,19 +11092,19 @@
       <c r="A161">
         <v>1</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C161" s="2">
+      <c r="B161" t="s">
+        <v>8</v>
+      </c>
+      <c r="C161" s="1">
         <v>46174</v>
       </c>
       <c r="D161">
         <v>2026</v>
       </c>
-      <c r="E161" s="1" t="s">
+      <c r="E161" t="s">
         <v>13</v>
       </c>
-      <c r="F161" s="1" t="s">
+      <c r="F161" t="s">
         <v>12</v>
       </c>
       <c r="G161">
@@ -11193,19 +11118,19 @@
       <c r="A162">
         <v>2</v>
       </c>
-      <c r="B162" s="1" t="s">
+      <c r="B162" t="s">
         <v>14</v>
       </c>
-      <c r="C162" s="2">
+      <c r="C162" s="1">
         <v>44197</v>
       </c>
       <c r="D162">
         <v>2021</v>
       </c>
-      <c r="E162" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F162" s="1" t="s">
+      <c r="E162" t="s">
+        <v>9</v>
+      </c>
+      <c r="F162" t="s">
         <v>10</v>
       </c>
       <c r="G162">
@@ -11219,19 +11144,19 @@
       <c r="A163">
         <v>2</v>
       </c>
-      <c r="B163" s="1" t="s">
+      <c r="B163" t="s">
         <v>14</v>
       </c>
-      <c r="C163" s="2">
+      <c r="C163" s="1">
         <v>44197</v>
       </c>
       <c r="D163">
         <v>2021</v>
       </c>
-      <c r="E163" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F163" s="1" t="s">
+      <c r="E163" t="s">
+        <v>9</v>
+      </c>
+      <c r="F163" t="s">
         <v>11</v>
       </c>
       <c r="G163">
@@ -11245,19 +11170,19 @@
       <c r="A164">
         <v>2</v>
       </c>
-      <c r="B164" s="1" t="s">
+      <c r="B164" t="s">
         <v>14</v>
       </c>
-      <c r="C164" s="2">
+      <c r="C164" s="1">
         <v>44197</v>
       </c>
       <c r="D164">
         <v>2021</v>
       </c>
-      <c r="E164" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F164" s="1" t="s">
+      <c r="E164" t="s">
+        <v>9</v>
+      </c>
+      <c r="F164" t="s">
         <v>12</v>
       </c>
       <c r="G164">
@@ -11271,19 +11196,19 @@
       <c r="A165">
         <v>2</v>
       </c>
-      <c r="B165" s="1" t="s">
+      <c r="B165" t="s">
         <v>14</v>
       </c>
-      <c r="C165" s="2">
+      <c r="C165" s="1">
         <v>44287</v>
       </c>
       <c r="D165">
         <v>2021</v>
       </c>
-      <c r="E165" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F165" s="1" t="s">
+      <c r="E165" t="s">
+        <v>9</v>
+      </c>
+      <c r="F165" t="s">
         <v>10</v>
       </c>
       <c r="G165">
@@ -11297,19 +11222,19 @@
       <c r="A166">
         <v>2</v>
       </c>
-      <c r="B166" s="1" t="s">
+      <c r="B166" t="s">
         <v>14</v>
       </c>
-      <c r="C166" s="2">
+      <c r="C166" s="1">
         <v>44287</v>
       </c>
       <c r="D166">
         <v>2021</v>
       </c>
-      <c r="E166" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F166" s="1" t="s">
+      <c r="E166" t="s">
+        <v>9</v>
+      </c>
+      <c r="F166" t="s">
         <v>11</v>
       </c>
       <c r="G166">
@@ -11323,19 +11248,19 @@
       <c r="A167">
         <v>2</v>
       </c>
-      <c r="B167" s="1" t="s">
+      <c r="B167" t="s">
         <v>14</v>
       </c>
-      <c r="C167" s="2">
+      <c r="C167" s="1">
         <v>44287</v>
       </c>
       <c r="D167">
         <v>2021</v>
       </c>
-      <c r="E167" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F167" s="1" t="s">
+      <c r="E167" t="s">
+        <v>9</v>
+      </c>
+      <c r="F167" t="s">
         <v>12</v>
       </c>
       <c r="G167">
@@ -11349,19 +11274,19 @@
       <c r="A168">
         <v>2</v>
       </c>
-      <c r="B168" s="1" t="s">
+      <c r="B168" t="s">
         <v>14</v>
       </c>
-      <c r="C168" s="2">
+      <c r="C168" s="1">
         <v>44378</v>
       </c>
       <c r="D168">
         <v>2021</v>
       </c>
-      <c r="E168" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F168" s="1" t="s">
+      <c r="E168" t="s">
+        <v>9</v>
+      </c>
+      <c r="F168" t="s">
         <v>10</v>
       </c>
       <c r="G168">
@@ -11375,19 +11300,19 @@
       <c r="A169">
         <v>2</v>
       </c>
-      <c r="B169" s="1" t="s">
+      <c r="B169" t="s">
         <v>14</v>
       </c>
-      <c r="C169" s="2">
+      <c r="C169" s="1">
         <v>44378</v>
       </c>
       <c r="D169">
         <v>2021</v>
       </c>
-      <c r="E169" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F169" s="1" t="s">
+      <c r="E169" t="s">
+        <v>9</v>
+      </c>
+      <c r="F169" t="s">
         <v>11</v>
       </c>
       <c r="G169">
@@ -11401,19 +11326,19 @@
       <c r="A170">
         <v>2</v>
       </c>
-      <c r="B170" s="1" t="s">
+      <c r="B170" t="s">
         <v>14</v>
       </c>
-      <c r="C170" s="2">
+      <c r="C170" s="1">
         <v>44378</v>
       </c>
       <c r="D170">
         <v>2021</v>
       </c>
-      <c r="E170" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F170" s="1" t="s">
+      <c r="E170" t="s">
+        <v>9</v>
+      </c>
+      <c r="F170" t="s">
         <v>12</v>
       </c>
       <c r="G170">
@@ -11427,19 +11352,19 @@
       <c r="A171">
         <v>2</v>
       </c>
-      <c r="B171" s="1" t="s">
+      <c r="B171" t="s">
         <v>14</v>
       </c>
-      <c r="C171" s="2">
+      <c r="C171" s="1">
         <v>44470</v>
       </c>
       <c r="D171">
         <v>2021</v>
       </c>
-      <c r="E171" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F171" s="1" t="s">
+      <c r="E171" t="s">
+        <v>9</v>
+      </c>
+      <c r="F171" t="s">
         <v>10</v>
       </c>
       <c r="G171">
@@ -11453,19 +11378,19 @@
       <c r="A172">
         <v>2</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="B172" t="s">
         <v>14</v>
       </c>
-      <c r="C172" s="2">
+      <c r="C172" s="1">
         <v>44470</v>
       </c>
       <c r="D172">
         <v>2021</v>
       </c>
-      <c r="E172" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F172" s="1" t="s">
+      <c r="E172" t="s">
+        <v>9</v>
+      </c>
+      <c r="F172" t="s">
         <v>11</v>
       </c>
       <c r="G172">
@@ -11479,19 +11404,19 @@
       <c r="A173">
         <v>2</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="B173" t="s">
         <v>14</v>
       </c>
-      <c r="C173" s="2">
+      <c r="C173" s="1">
         <v>44470</v>
       </c>
       <c r="D173">
         <v>2021</v>
       </c>
-      <c r="E173" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F173" s="1" t="s">
+      <c r="E173" t="s">
+        <v>9</v>
+      </c>
+      <c r="F173" t="s">
         <v>12</v>
       </c>
       <c r="G173">
@@ -11505,19 +11430,19 @@
       <c r="A174">
         <v>2</v>
       </c>
-      <c r="B174" s="1" t="s">
+      <c r="B174" t="s">
         <v>14</v>
       </c>
-      <c r="C174" s="2">
+      <c r="C174" s="1">
         <v>44562</v>
       </c>
       <c r="D174">
         <v>2022</v>
       </c>
-      <c r="E174" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F174" s="1" t="s">
+      <c r="E174" t="s">
+        <v>9</v>
+      </c>
+      <c r="F174" t="s">
         <v>10</v>
       </c>
       <c r="G174">
@@ -11531,19 +11456,19 @@
       <c r="A175">
         <v>2</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="B175" t="s">
         <v>14</v>
       </c>
-      <c r="C175" s="2">
+      <c r="C175" s="1">
         <v>44562</v>
       </c>
       <c r="D175">
         <v>2022</v>
       </c>
-      <c r="E175" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F175" s="1" t="s">
+      <c r="E175" t="s">
+        <v>9</v>
+      </c>
+      <c r="F175" t="s">
         <v>11</v>
       </c>
       <c r="G175">
@@ -11557,19 +11482,19 @@
       <c r="A176">
         <v>2</v>
       </c>
-      <c r="B176" s="1" t="s">
+      <c r="B176" t="s">
         <v>14</v>
       </c>
-      <c r="C176" s="2">
+      <c r="C176" s="1">
         <v>44562</v>
       </c>
       <c r="D176">
         <v>2022</v>
       </c>
-      <c r="E176" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F176" s="1" t="s">
+      <c r="E176" t="s">
+        <v>9</v>
+      </c>
+      <c r="F176" t="s">
         <v>12</v>
       </c>
       <c r="G176">
@@ -11583,19 +11508,19 @@
       <c r="A177">
         <v>2</v>
       </c>
-      <c r="B177" s="1" t="s">
+      <c r="B177" t="s">
         <v>14</v>
       </c>
-      <c r="C177" s="2">
+      <c r="C177" s="1">
         <v>44652</v>
       </c>
       <c r="D177">
         <v>2022</v>
       </c>
-      <c r="E177" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F177" s="1" t="s">
+      <c r="E177" t="s">
+        <v>9</v>
+      </c>
+      <c r="F177" t="s">
         <v>10</v>
       </c>
       <c r="G177">
@@ -11609,19 +11534,19 @@
       <c r="A178">
         <v>2</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="B178" t="s">
         <v>14</v>
       </c>
-      <c r="C178" s="2">
+      <c r="C178" s="1">
         <v>44652</v>
       </c>
       <c r="D178">
         <v>2022</v>
       </c>
-      <c r="E178" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F178" s="1" t="s">
+      <c r="E178" t="s">
+        <v>9</v>
+      </c>
+      <c r="F178" t="s">
         <v>11</v>
       </c>
       <c r="G178">
@@ -11635,19 +11560,19 @@
       <c r="A179">
         <v>2</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="B179" t="s">
         <v>14</v>
       </c>
-      <c r="C179" s="2">
+      <c r="C179" s="1">
         <v>44652</v>
       </c>
       <c r="D179">
         <v>2022</v>
       </c>
-      <c r="E179" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F179" s="1" t="s">
+      <c r="E179" t="s">
+        <v>9</v>
+      </c>
+      <c r="F179" t="s">
         <v>12</v>
       </c>
       <c r="G179">
@@ -11661,19 +11586,19 @@
       <c r="A180">
         <v>2</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="B180" t="s">
         <v>14</v>
       </c>
-      <c r="C180" s="2">
+      <c r="C180" s="1">
         <v>44743</v>
       </c>
       <c r="D180">
         <v>2022</v>
       </c>
-      <c r="E180" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F180" s="1" t="s">
+      <c r="E180" t="s">
+        <v>9</v>
+      </c>
+      <c r="F180" t="s">
         <v>10</v>
       </c>
       <c r="G180">
@@ -11687,19 +11612,19 @@
       <c r="A181">
         <v>2</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="B181" t="s">
         <v>14</v>
       </c>
-      <c r="C181" s="2">
+      <c r="C181" s="1">
         <v>44743</v>
       </c>
       <c r="D181">
         <v>2022</v>
       </c>
-      <c r="E181" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F181" s="1" t="s">
+      <c r="E181" t="s">
+        <v>9</v>
+      </c>
+      <c r="F181" t="s">
         <v>11</v>
       </c>
       <c r="G181">
@@ -11713,19 +11638,19 @@
       <c r="A182">
         <v>2</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="B182" t="s">
         <v>14</v>
       </c>
-      <c r="C182" s="2">
+      <c r="C182" s="1">
         <v>44743</v>
       </c>
       <c r="D182">
         <v>2022</v>
       </c>
-      <c r="E182" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F182" s="1" t="s">
+      <c r="E182" t="s">
+        <v>9</v>
+      </c>
+      <c r="F182" t="s">
         <v>12</v>
       </c>
       <c r="G182">
@@ -11739,19 +11664,19 @@
       <c r="A183">
         <v>2</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="B183" t="s">
         <v>14</v>
       </c>
-      <c r="C183" s="2">
+      <c r="C183" s="1">
         <v>44835</v>
       </c>
       <c r="D183">
         <v>2022</v>
       </c>
-      <c r="E183" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F183" s="1" t="s">
+      <c r="E183" t="s">
+        <v>9</v>
+      </c>
+      <c r="F183" t="s">
         <v>10</v>
       </c>
       <c r="G183">
@@ -11765,19 +11690,19 @@
       <c r="A184">
         <v>2</v>
       </c>
-      <c r="B184" s="1" t="s">
+      <c r="B184" t="s">
         <v>14</v>
       </c>
-      <c r="C184" s="2">
+      <c r="C184" s="1">
         <v>44835</v>
       </c>
       <c r="D184">
         <v>2022</v>
       </c>
-      <c r="E184" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F184" s="1" t="s">
+      <c r="E184" t="s">
+        <v>9</v>
+      </c>
+      <c r="F184" t="s">
         <v>11</v>
       </c>
       <c r="G184">
@@ -11791,19 +11716,19 @@
       <c r="A185">
         <v>2</v>
       </c>
-      <c r="B185" s="1" t="s">
+      <c r="B185" t="s">
         <v>14</v>
       </c>
-      <c r="C185" s="2">
+      <c r="C185" s="1">
         <v>44835</v>
       </c>
       <c r="D185">
         <v>2022</v>
       </c>
-      <c r="E185" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F185" s="1" t="s">
+      <c r="E185" t="s">
+        <v>9</v>
+      </c>
+      <c r="F185" t="s">
         <v>12</v>
       </c>
       <c r="G185">
@@ -11817,19 +11742,19 @@
       <c r="A186">
         <v>2</v>
       </c>
-      <c r="B186" s="1" t="s">
+      <c r="B186" t="s">
         <v>14</v>
       </c>
-      <c r="C186" s="2">
+      <c r="C186" s="1">
         <v>44927</v>
       </c>
       <c r="D186">
         <v>2023</v>
       </c>
-      <c r="E186" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F186" s="1" t="s">
+      <c r="E186" t="s">
+        <v>9</v>
+      </c>
+      <c r="F186" t="s">
         <v>10</v>
       </c>
       <c r="G186">
@@ -11843,19 +11768,19 @@
       <c r="A187">
         <v>2</v>
       </c>
-      <c r="B187" s="1" t="s">
+      <c r="B187" t="s">
         <v>14</v>
       </c>
-      <c r="C187" s="2">
+      <c r="C187" s="1">
         <v>44927</v>
       </c>
       <c r="D187">
         <v>2023</v>
       </c>
-      <c r="E187" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F187" s="1" t="s">
+      <c r="E187" t="s">
+        <v>9</v>
+      </c>
+      <c r="F187" t="s">
         <v>11</v>
       </c>
       <c r="G187">
@@ -11869,19 +11794,19 @@
       <c r="A188">
         <v>2</v>
       </c>
-      <c r="B188" s="1" t="s">
+      <c r="B188" t="s">
         <v>14</v>
       </c>
-      <c r="C188" s="2">
+      <c r="C188" s="1">
         <v>44927</v>
       </c>
       <c r="D188">
         <v>2023</v>
       </c>
-      <c r="E188" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F188" s="1" t="s">
+      <c r="E188" t="s">
+        <v>9</v>
+      </c>
+      <c r="F188" t="s">
         <v>12</v>
       </c>
       <c r="G188">
@@ -11895,19 +11820,19 @@
       <c r="A189">
         <v>2</v>
       </c>
-      <c r="B189" s="1" t="s">
+      <c r="B189" t="s">
         <v>14</v>
       </c>
-      <c r="C189" s="2">
+      <c r="C189" s="1">
         <v>45017</v>
       </c>
       <c r="D189">
         <v>2023</v>
       </c>
-      <c r="E189" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F189" s="1" t="s">
+      <c r="E189" t="s">
+        <v>9</v>
+      </c>
+      <c r="F189" t="s">
         <v>10</v>
       </c>
       <c r="G189">
@@ -11921,19 +11846,19 @@
       <c r="A190">
         <v>2</v>
       </c>
-      <c r="B190" s="1" t="s">
+      <c r="B190" t="s">
         <v>14</v>
       </c>
-      <c r="C190" s="2">
+      <c r="C190" s="1">
         <v>45017</v>
       </c>
       <c r="D190">
         <v>2023</v>
       </c>
-      <c r="E190" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F190" s="1" t="s">
+      <c r="E190" t="s">
+        <v>9</v>
+      </c>
+      <c r="F190" t="s">
         <v>11</v>
       </c>
       <c r="G190">
@@ -11947,19 +11872,19 @@
       <c r="A191">
         <v>2</v>
       </c>
-      <c r="B191" s="1" t="s">
+      <c r="B191" t="s">
         <v>14</v>
       </c>
-      <c r="C191" s="2">
+      <c r="C191" s="1">
         <v>45017</v>
       </c>
       <c r="D191">
         <v>2023</v>
       </c>
-      <c r="E191" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F191" s="1" t="s">
+      <c r="E191" t="s">
+        <v>9</v>
+      </c>
+      <c r="F191" t="s">
         <v>12</v>
       </c>
       <c r="G191">
@@ -11973,19 +11898,19 @@
       <c r="A192">
         <v>2</v>
       </c>
-      <c r="B192" s="1" t="s">
+      <c r="B192" t="s">
         <v>14</v>
       </c>
-      <c r="C192" s="2">
+      <c r="C192" s="1">
         <v>45108</v>
       </c>
       <c r="D192">
         <v>2023</v>
       </c>
-      <c r="E192" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F192" s="1" t="s">
+      <c r="E192" t="s">
+        <v>9</v>
+      </c>
+      <c r="F192" t="s">
         <v>10</v>
       </c>
       <c r="G192">
@@ -11999,19 +11924,19 @@
       <c r="A193">
         <v>2</v>
       </c>
-      <c r="B193" s="1" t="s">
+      <c r="B193" t="s">
         <v>14</v>
       </c>
-      <c r="C193" s="2">
+      <c r="C193" s="1">
         <v>45108</v>
       </c>
       <c r="D193">
         <v>2023</v>
       </c>
-      <c r="E193" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F193" s="1" t="s">
+      <c r="E193" t="s">
+        <v>9</v>
+      </c>
+      <c r="F193" t="s">
         <v>11</v>
       </c>
       <c r="G193">
@@ -12025,19 +11950,19 @@
       <c r="A194">
         <v>2</v>
       </c>
-      <c r="B194" s="1" t="s">
+      <c r="B194" t="s">
         <v>14</v>
       </c>
-      <c r="C194" s="2">
+      <c r="C194" s="1">
         <v>45108</v>
       </c>
       <c r="D194">
         <v>2023</v>
       </c>
-      <c r="E194" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F194" s="1" t="s">
+      <c r="E194" t="s">
+        <v>9</v>
+      </c>
+      <c r="F194" t="s">
         <v>12</v>
       </c>
       <c r="G194">
@@ -12051,19 +11976,19 @@
       <c r="A195">
         <v>2</v>
       </c>
-      <c r="B195" s="1" t="s">
+      <c r="B195" t="s">
         <v>14</v>
       </c>
-      <c r="C195" s="2">
+      <c r="C195" s="1">
         <v>45200</v>
       </c>
       <c r="D195">
         <v>2023</v>
       </c>
-      <c r="E195" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F195" s="1" t="s">
+      <c r="E195" t="s">
+        <v>9</v>
+      </c>
+      <c r="F195" t="s">
         <v>10</v>
       </c>
       <c r="G195">
@@ -12077,19 +12002,19 @@
       <c r="A196">
         <v>2</v>
       </c>
-      <c r="B196" s="1" t="s">
+      <c r="B196" t="s">
         <v>14</v>
       </c>
-      <c r="C196" s="2">
+      <c r="C196" s="1">
         <v>45200</v>
       </c>
       <c r="D196">
         <v>2023</v>
       </c>
-      <c r="E196" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F196" s="1" t="s">
+      <c r="E196" t="s">
+        <v>9</v>
+      </c>
+      <c r="F196" t="s">
         <v>11</v>
       </c>
       <c r="G196">
@@ -12103,19 +12028,19 @@
       <c r="A197">
         <v>2</v>
       </c>
-      <c r="B197" s="1" t="s">
+      <c r="B197" t="s">
         <v>14</v>
       </c>
-      <c r="C197" s="2">
+      <c r="C197" s="1">
         <v>45200</v>
       </c>
       <c r="D197">
         <v>2023</v>
       </c>
-      <c r="E197" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F197" s="1" t="s">
+      <c r="E197" t="s">
+        <v>9</v>
+      </c>
+      <c r="F197" t="s">
         <v>12</v>
       </c>
       <c r="G197">
@@ -12129,19 +12054,19 @@
       <c r="A198">
         <v>2</v>
       </c>
-      <c r="B198" s="1" t="s">
+      <c r="B198" t="s">
         <v>14</v>
       </c>
-      <c r="C198" s="2">
+      <c r="C198" s="1">
         <v>45292</v>
       </c>
       <c r="D198">
         <v>2024</v>
       </c>
-      <c r="E198" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F198" s="1" t="s">
+      <c r="E198" t="s">
+        <v>9</v>
+      </c>
+      <c r="F198" t="s">
         <v>10</v>
       </c>
       <c r="G198">
@@ -12155,19 +12080,19 @@
       <c r="A199">
         <v>2</v>
       </c>
-      <c r="B199" s="1" t="s">
+      <c r="B199" t="s">
         <v>14</v>
       </c>
-      <c r="C199" s="2">
+      <c r="C199" s="1">
         <v>45292</v>
       </c>
       <c r="D199">
         <v>2024</v>
       </c>
-      <c r="E199" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F199" s="1" t="s">
+      <c r="E199" t="s">
+        <v>9</v>
+      </c>
+      <c r="F199" t="s">
         <v>11</v>
       </c>
       <c r="G199">
@@ -12181,19 +12106,19 @@
       <c r="A200">
         <v>2</v>
       </c>
-      <c r="B200" s="1" t="s">
+      <c r="B200" t="s">
         <v>14</v>
       </c>
-      <c r="C200" s="2">
+      <c r="C200" s="1">
         <v>45292</v>
       </c>
       <c r="D200">
         <v>2024</v>
       </c>
-      <c r="E200" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F200" s="1" t="s">
+      <c r="E200" t="s">
+        <v>9</v>
+      </c>
+      <c r="F200" t="s">
         <v>12</v>
       </c>
       <c r="G200">
@@ -12207,19 +12132,19 @@
       <c r="A201">
         <v>2</v>
       </c>
-      <c r="B201" s="1" t="s">
+      <c r="B201" t="s">
         <v>14</v>
       </c>
-      <c r="C201" s="2">
+      <c r="C201" s="1">
         <v>45383</v>
       </c>
       <c r="D201">
         <v>2024</v>
       </c>
-      <c r="E201" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F201" s="1" t="s">
+      <c r="E201" t="s">
+        <v>9</v>
+      </c>
+      <c r="F201" t="s">
         <v>10</v>
       </c>
       <c r="G201">
@@ -12233,19 +12158,19 @@
       <c r="A202">
         <v>2</v>
       </c>
-      <c r="B202" s="1" t="s">
+      <c r="B202" t="s">
         <v>14</v>
       </c>
-      <c r="C202" s="2">
+      <c r="C202" s="1">
         <v>45383</v>
       </c>
       <c r="D202">
         <v>2024</v>
       </c>
-      <c r="E202" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F202" s="1" t="s">
+      <c r="E202" t="s">
+        <v>9</v>
+      </c>
+      <c r="F202" t="s">
         <v>11</v>
       </c>
       <c r="G202">
@@ -12259,19 +12184,19 @@
       <c r="A203">
         <v>2</v>
       </c>
-      <c r="B203" s="1" t="s">
+      <c r="B203" t="s">
         <v>14</v>
       </c>
-      <c r="C203" s="2">
+      <c r="C203" s="1">
         <v>45383</v>
       </c>
       <c r="D203">
         <v>2024</v>
       </c>
-      <c r="E203" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F203" s="1" t="s">
+      <c r="E203" t="s">
+        <v>9</v>
+      </c>
+      <c r="F203" t="s">
         <v>12</v>
       </c>
       <c r="G203">
@@ -12285,19 +12210,19 @@
       <c r="A204">
         <v>2</v>
       </c>
-      <c r="B204" s="1" t="s">
+      <c r="B204" t="s">
         <v>14</v>
       </c>
-      <c r="C204" s="2">
+      <c r="C204" s="1">
         <v>45474</v>
       </c>
       <c r="D204">
         <v>2024</v>
       </c>
-      <c r="E204" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F204" s="1" t="s">
+      <c r="E204" t="s">
+        <v>9</v>
+      </c>
+      <c r="F204" t="s">
         <v>10</v>
       </c>
       <c r="G204">
@@ -12311,19 +12236,19 @@
       <c r="A205">
         <v>2</v>
       </c>
-      <c r="B205" s="1" t="s">
+      <c r="B205" t="s">
         <v>14</v>
       </c>
-      <c r="C205" s="2">
+      <c r="C205" s="1">
         <v>45474</v>
       </c>
       <c r="D205">
         <v>2024</v>
       </c>
-      <c r="E205" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F205" s="1" t="s">
+      <c r="E205" t="s">
+        <v>9</v>
+      </c>
+      <c r="F205" t="s">
         <v>11</v>
       </c>
       <c r="G205">
@@ -12337,19 +12262,19 @@
       <c r="A206">
         <v>2</v>
       </c>
-      <c r="B206" s="1" t="s">
+      <c r="B206" t="s">
         <v>14</v>
       </c>
-      <c r="C206" s="2">
+      <c r="C206" s="1">
         <v>45474</v>
       </c>
       <c r="D206">
         <v>2024</v>
       </c>
-      <c r="E206" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F206" s="1" t="s">
+      <c r="E206" t="s">
+        <v>9</v>
+      </c>
+      <c r="F206" t="s">
         <v>12</v>
       </c>
       <c r="G206">
@@ -12363,19 +12288,19 @@
       <c r="A207">
         <v>2</v>
       </c>
-      <c r="B207" s="1" t="s">
+      <c r="B207" t="s">
         <v>14</v>
       </c>
-      <c r="C207" s="2">
+      <c r="C207" s="1">
         <v>45566</v>
       </c>
       <c r="D207">
         <v>2024</v>
       </c>
-      <c r="E207" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F207" s="1" t="s">
+      <c r="E207" t="s">
+        <v>9</v>
+      </c>
+      <c r="F207" t="s">
         <v>10</v>
       </c>
       <c r="G207">
@@ -12389,19 +12314,19 @@
       <c r="A208">
         <v>2</v>
       </c>
-      <c r="B208" s="1" t="s">
+      <c r="B208" t="s">
         <v>14</v>
       </c>
-      <c r="C208" s="2">
+      <c r="C208" s="1">
         <v>45566</v>
       </c>
       <c r="D208">
         <v>2024</v>
       </c>
-      <c r="E208" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F208" s="1" t="s">
+      <c r="E208" t="s">
+        <v>9</v>
+      </c>
+      <c r="F208" t="s">
         <v>11</v>
       </c>
       <c r="G208">
@@ -12415,19 +12340,19 @@
       <c r="A209">
         <v>2</v>
       </c>
-      <c r="B209" s="1" t="s">
+      <c r="B209" t="s">
         <v>14</v>
       </c>
-      <c r="C209" s="2">
+      <c r="C209" s="1">
         <v>45566</v>
       </c>
       <c r="D209">
         <v>2024</v>
       </c>
-      <c r="E209" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F209" s="1" t="s">
+      <c r="E209" t="s">
+        <v>9</v>
+      </c>
+      <c r="F209" t="s">
         <v>12</v>
       </c>
       <c r="G209">
@@ -12441,19 +12366,19 @@
       <c r="A210">
         <v>2</v>
       </c>
-      <c r="B210" s="1" t="s">
+      <c r="B210" t="s">
         <v>14</v>
       </c>
-      <c r="C210" s="2">
+      <c r="C210" s="1">
         <v>45658</v>
       </c>
       <c r="D210">
         <v>2025</v>
       </c>
-      <c r="E210" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F210" s="1" t="s">
+      <c r="E210" t="s">
+        <v>9</v>
+      </c>
+      <c r="F210" t="s">
         <v>11</v>
       </c>
       <c r="G210">
@@ -12467,19 +12392,19 @@
       <c r="A211">
         <v>2</v>
       </c>
-      <c r="B211" s="1" t="s">
+      <c r="B211" t="s">
         <v>14</v>
       </c>
-      <c r="C211" s="2">
+      <c r="C211" s="1">
         <v>45658</v>
       </c>
       <c r="D211">
         <v>2025</v>
       </c>
-      <c r="E211" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F211" s="1" t="s">
+      <c r="E211" t="s">
+        <v>9</v>
+      </c>
+      <c r="F211" t="s">
         <v>12</v>
       </c>
       <c r="G211">
@@ -12493,19 +12418,19 @@
       <c r="A212">
         <v>2</v>
       </c>
-      <c r="B212" s="1" t="s">
+      <c r="B212" t="s">
         <v>14</v>
       </c>
-      <c r="C212" s="2">
+      <c r="C212" s="1">
         <v>45748</v>
       </c>
       <c r="D212">
         <v>2025</v>
       </c>
-      <c r="E212" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F212" s="1" t="s">
+      <c r="E212" t="s">
+        <v>9</v>
+      </c>
+      <c r="F212" t="s">
         <v>10</v>
       </c>
       <c r="G212">
@@ -12519,19 +12444,19 @@
       <c r="A213">
         <v>2</v>
       </c>
-      <c r="B213" s="1" t="s">
+      <c r="B213" t="s">
         <v>14</v>
       </c>
-      <c r="C213" s="2">
+      <c r="C213" s="1">
         <v>45748</v>
       </c>
       <c r="D213">
         <v>2025</v>
       </c>
-      <c r="E213" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F213" s="1" t="s">
+      <c r="E213" t="s">
+        <v>9</v>
+      </c>
+      <c r="F213" t="s">
         <v>11</v>
       </c>
       <c r="G213">
@@ -12545,19 +12470,19 @@
       <c r="A214">
         <v>2</v>
       </c>
-      <c r="B214" s="1" t="s">
+      <c r="B214" t="s">
         <v>14</v>
       </c>
-      <c r="C214" s="2">
+      <c r="C214" s="1">
         <v>45748</v>
       </c>
       <c r="D214">
         <v>2025</v>
       </c>
-      <c r="E214" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F214" s="1" t="s">
+      <c r="E214" t="s">
+        <v>9</v>
+      </c>
+      <c r="F214" t="s">
         <v>12</v>
       </c>
       <c r="G214">
@@ -12571,19 +12496,19 @@
       <c r="A215">
         <v>2</v>
       </c>
-      <c r="B215" s="1" t="s">
+      <c r="B215" t="s">
         <v>14</v>
       </c>
-      <c r="C215" s="2">
+      <c r="C215" s="1">
         <v>45839</v>
       </c>
       <c r="D215">
         <v>2025</v>
       </c>
-      <c r="E215" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F215" s="1" t="s">
+      <c r="E215" t="s">
+        <v>9</v>
+      </c>
+      <c r="F215" t="s">
         <v>10</v>
       </c>
       <c r="G215">
@@ -12597,19 +12522,19 @@
       <c r="A216">
         <v>2</v>
       </c>
-      <c r="B216" s="1" t="s">
+      <c r="B216" t="s">
         <v>14</v>
       </c>
-      <c r="C216" s="2">
+      <c r="C216" s="1">
         <v>45839</v>
       </c>
       <c r="D216">
         <v>2025</v>
       </c>
-      <c r="E216" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F216" s="1" t="s">
+      <c r="E216" t="s">
+        <v>9</v>
+      </c>
+      <c r="F216" t="s">
         <v>11</v>
       </c>
       <c r="G216">
@@ -12623,19 +12548,19 @@
       <c r="A217">
         <v>2</v>
       </c>
-      <c r="B217" s="1" t="s">
+      <c r="B217" t="s">
         <v>14</v>
       </c>
-      <c r="C217" s="2">
+      <c r="C217" s="1">
         <v>45839</v>
       </c>
       <c r="D217">
         <v>2025</v>
       </c>
-      <c r="E217" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F217" s="1" t="s">
+      <c r="E217" t="s">
+        <v>9</v>
+      </c>
+      <c r="F217" t="s">
         <v>12</v>
       </c>
       <c r="G217">
@@ -12649,19 +12574,19 @@
       <c r="A218">
         <v>2</v>
       </c>
-      <c r="B218" s="1" t="s">
+      <c r="B218" t="s">
         <v>14</v>
       </c>
-      <c r="C218" s="2">
+      <c r="C218" s="1">
         <v>45931</v>
       </c>
       <c r="D218">
         <v>2025</v>
       </c>
-      <c r="E218" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F218" s="1" t="s">
+      <c r="E218" t="s">
+        <v>9</v>
+      </c>
+      <c r="F218" t="s">
         <v>10</v>
       </c>
       <c r="G218">
@@ -12675,19 +12600,19 @@
       <c r="A219">
         <v>2</v>
       </c>
-      <c r="B219" s="1" t="s">
+      <c r="B219" t="s">
         <v>14</v>
       </c>
-      <c r="C219" s="2">
+      <c r="C219" s="1">
         <v>45931</v>
       </c>
       <c r="D219">
         <v>2025</v>
       </c>
-      <c r="E219" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F219" s="1" t="s">
+      <c r="E219" t="s">
+        <v>9</v>
+      </c>
+      <c r="F219" t="s">
         <v>11</v>
       </c>
       <c r="G219">
@@ -12701,19 +12626,19 @@
       <c r="A220">
         <v>2</v>
       </c>
-      <c r="B220" s="1" t="s">
+      <c r="B220" t="s">
         <v>14</v>
       </c>
-      <c r="C220" s="2">
+      <c r="C220" s="1">
         <v>45931</v>
       </c>
       <c r="D220">
         <v>2025</v>
       </c>
-      <c r="E220" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F220" s="1" t="s">
+      <c r="E220" t="s">
+        <v>9</v>
+      </c>
+      <c r="F220" t="s">
         <v>12</v>
       </c>
       <c r="G220">
@@ -12727,19 +12652,19 @@
       <c r="A221">
         <v>2</v>
       </c>
-      <c r="B221" s="1" t="s">
+      <c r="B221" t="s">
         <v>14</v>
       </c>
-      <c r="C221" s="2">
+      <c r="C221" s="1">
         <v>46023</v>
       </c>
       <c r="D221">
         <v>2026</v>
       </c>
-      <c r="E221" s="1" t="s">
+      <c r="E221" t="s">
         <v>13</v>
       </c>
-      <c r="F221" s="1" t="s">
+      <c r="F221" t="s">
         <v>11</v>
       </c>
       <c r="G221">
@@ -12753,19 +12678,19 @@
       <c r="A222">
         <v>2</v>
       </c>
-      <c r="B222" s="1" t="s">
+      <c r="B222" t="s">
         <v>14</v>
       </c>
-      <c r="C222" s="2">
+      <c r="C222" s="1">
         <v>46023</v>
       </c>
       <c r="D222">
         <v>2026</v>
       </c>
-      <c r="E222" s="1" t="s">
+      <c r="E222" t="s">
         <v>13</v>
       </c>
-      <c r="F222" s="1" t="s">
+      <c r="F222" t="s">
         <v>12</v>
       </c>
       <c r="G222">
@@ -12779,19 +12704,19 @@
       <c r="A223">
         <v>2</v>
       </c>
-      <c r="B223" s="1" t="s">
+      <c r="B223" t="s">
         <v>14</v>
       </c>
-      <c r="C223" s="2">
+      <c r="C223" s="1">
         <v>46113</v>
       </c>
       <c r="D223">
         <v>2026</v>
       </c>
-      <c r="E223" s="1" t="s">
+      <c r="E223" t="s">
         <v>13</v>
       </c>
-      <c r="F223" s="1" t="s">
+      <c r="F223" t="s">
         <v>10</v>
       </c>
       <c r="G223">
@@ -12805,19 +12730,19 @@
       <c r="A224">
         <v>2</v>
       </c>
-      <c r="B224" s="1" t="s">
+      <c r="B224" t="s">
         <v>14</v>
       </c>
-      <c r="C224" s="2">
+      <c r="C224" s="1">
         <v>46113</v>
       </c>
       <c r="D224">
         <v>2026</v>
       </c>
-      <c r="E224" s="1" t="s">
+      <c r="E224" t="s">
         <v>13</v>
       </c>
-      <c r="F224" s="1" t="s">
+      <c r="F224" t="s">
         <v>11</v>
       </c>
       <c r="G224">
@@ -12831,19 +12756,19 @@
       <c r="A225">
         <v>2</v>
       </c>
-      <c r="B225" s="1" t="s">
+      <c r="B225" t="s">
         <v>14</v>
       </c>
-      <c r="C225" s="2">
+      <c r="C225" s="1">
         <v>46113</v>
       </c>
       <c r="D225">
         <v>2026</v>
       </c>
-      <c r="E225" s="1" t="s">
+      <c r="E225" t="s">
         <v>13</v>
       </c>
-      <c r="F225" s="1" t="s">
+      <c r="F225" t="s">
         <v>12</v>
       </c>
       <c r="G225">
@@ -12857,19 +12782,19 @@
       <c r="A226">
         <v>3</v>
       </c>
-      <c r="B226" s="1" t="s">
+      <c r="B226" t="s">
         <v>15</v>
       </c>
-      <c r="C226" s="2">
+      <c r="C226" s="1">
         <v>44197</v>
       </c>
       <c r="D226">
         <v>2021</v>
       </c>
-      <c r="E226" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F226" s="1" t="s">
+      <c r="E226" t="s">
+        <v>9</v>
+      </c>
+      <c r="F226" t="s">
         <v>10</v>
       </c>
       <c r="G226">
@@ -12883,19 +12808,19 @@
       <c r="A227">
         <v>3</v>
       </c>
-      <c r="B227" s="1" t="s">
+      <c r="B227" t="s">
         <v>15</v>
       </c>
-      <c r="C227" s="2">
+      <c r="C227" s="1">
         <v>44197</v>
       </c>
       <c r="D227">
         <v>2021</v>
       </c>
-      <c r="E227" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F227" s="1" t="s">
+      <c r="E227" t="s">
+        <v>9</v>
+      </c>
+      <c r="F227" t="s">
         <v>11</v>
       </c>
       <c r="G227">
@@ -12909,19 +12834,19 @@
       <c r="A228">
         <v>3</v>
       </c>
-      <c r="B228" s="1" t="s">
+      <c r="B228" t="s">
         <v>15</v>
       </c>
-      <c r="C228" s="2">
+      <c r="C228" s="1">
         <v>44197</v>
       </c>
       <c r="D228">
         <v>2021</v>
       </c>
-      <c r="E228" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F228" s="1" t="s">
+      <c r="E228" t="s">
+        <v>9</v>
+      </c>
+      <c r="F228" t="s">
         <v>12</v>
       </c>
       <c r="G228">
@@ -12935,19 +12860,19 @@
       <c r="A229">
         <v>3</v>
       </c>
-      <c r="B229" s="1" t="s">
+      <c r="B229" t="s">
         <v>15</v>
       </c>
-      <c r="C229" s="2">
+      <c r="C229" s="1">
         <v>44562</v>
       </c>
       <c r="D229">
         <v>2022</v>
       </c>
-      <c r="E229" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F229" s="1" t="s">
+      <c r="E229" t="s">
+        <v>9</v>
+      </c>
+      <c r="F229" t="s">
         <v>10</v>
       </c>
       <c r="G229">
@@ -12961,19 +12886,19 @@
       <c r="A230">
         <v>3</v>
       </c>
-      <c r="B230" s="1" t="s">
+      <c r="B230" t="s">
         <v>15</v>
       </c>
-      <c r="C230" s="2">
+      <c r="C230" s="1">
         <v>44562</v>
       </c>
       <c r="D230">
         <v>2022</v>
       </c>
-      <c r="E230" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F230" s="1" t="s">
+      <c r="E230" t="s">
+        <v>9</v>
+      </c>
+      <c r="F230" t="s">
         <v>11</v>
       </c>
       <c r="G230">
@@ -12987,19 +12912,19 @@
       <c r="A231">
         <v>3</v>
       </c>
-      <c r="B231" s="1" t="s">
+      <c r="B231" t="s">
         <v>15</v>
       </c>
-      <c r="C231" s="2">
+      <c r="C231" s="1">
         <v>44562</v>
       </c>
       <c r="D231">
         <v>2022</v>
       </c>
-      <c r="E231" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F231" s="1" t="s">
+      <c r="E231" t="s">
+        <v>9</v>
+      </c>
+      <c r="F231" t="s">
         <v>12</v>
       </c>
       <c r="G231">
@@ -13013,19 +12938,19 @@
       <c r="A232">
         <v>3</v>
       </c>
-      <c r="B232" s="1" t="s">
+      <c r="B232" t="s">
         <v>15</v>
       </c>
-      <c r="C232" s="2">
+      <c r="C232" s="1">
         <v>44927</v>
       </c>
       <c r="D232">
         <v>2023</v>
       </c>
-      <c r="E232" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F232" s="1" t="s">
+      <c r="E232" t="s">
+        <v>9</v>
+      </c>
+      <c r="F232" t="s">
         <v>10</v>
       </c>
       <c r="G232">
@@ -13039,19 +12964,19 @@
       <c r="A233">
         <v>3</v>
       </c>
-      <c r="B233" s="1" t="s">
+      <c r="B233" t="s">
         <v>15</v>
       </c>
-      <c r="C233" s="2">
+      <c r="C233" s="1">
         <v>44927</v>
       </c>
       <c r="D233">
         <v>2023</v>
       </c>
-      <c r="E233" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F233" s="1" t="s">
+      <c r="E233" t="s">
+        <v>9</v>
+      </c>
+      <c r="F233" t="s">
         <v>11</v>
       </c>
       <c r="G233">
@@ -13065,19 +12990,19 @@
       <c r="A234">
         <v>3</v>
       </c>
-      <c r="B234" s="1" t="s">
+      <c r="B234" t="s">
         <v>15</v>
       </c>
-      <c r="C234" s="2">
+      <c r="C234" s="1">
         <v>44927</v>
       </c>
       <c r="D234">
         <v>2023</v>
       </c>
-      <c r="E234" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F234" s="1" t="s">
+      <c r="E234" t="s">
+        <v>9</v>
+      </c>
+      <c r="F234" t="s">
         <v>12</v>
       </c>
       <c r="G234">
@@ -13091,19 +13016,19 @@
       <c r="A235">
         <v>3</v>
       </c>
-      <c r="B235" s="1" t="s">
+      <c r="B235" t="s">
         <v>15</v>
       </c>
-      <c r="C235" s="2">
+      <c r="C235" s="1">
         <v>45292</v>
       </c>
       <c r="D235">
         <v>2024</v>
       </c>
-      <c r="E235" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F235" s="1" t="s">
+      <c r="E235" t="s">
+        <v>9</v>
+      </c>
+      <c r="F235" t="s">
         <v>10</v>
       </c>
       <c r="G235">
@@ -13117,19 +13042,19 @@
       <c r="A236">
         <v>3</v>
       </c>
-      <c r="B236" s="1" t="s">
+      <c r="B236" t="s">
         <v>15</v>
       </c>
-      <c r="C236" s="2">
+      <c r="C236" s="1">
         <v>45292</v>
       </c>
       <c r="D236">
         <v>2024</v>
       </c>
-      <c r="E236" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F236" s="1" t="s">
+      <c r="E236" t="s">
+        <v>9</v>
+      </c>
+      <c r="F236" t="s">
         <v>11</v>
       </c>
       <c r="G236">
@@ -13143,19 +13068,19 @@
       <c r="A237">
         <v>3</v>
       </c>
-      <c r="B237" s="1" t="s">
+      <c r="B237" t="s">
         <v>15</v>
       </c>
-      <c r="C237" s="2">
+      <c r="C237" s="1">
         <v>45292</v>
       </c>
       <c r="D237">
         <v>2024</v>
       </c>
-      <c r="E237" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F237" s="1" t="s">
+      <c r="E237" t="s">
+        <v>9</v>
+      </c>
+      <c r="F237" t="s">
         <v>12</v>
       </c>
       <c r="G237">
@@ -13169,19 +13094,19 @@
       <c r="A238">
         <v>3</v>
       </c>
-      <c r="B238" s="1" t="s">
+      <c r="B238" t="s">
         <v>15</v>
       </c>
-      <c r="C238" s="2">
+      <c r="C238" s="1">
         <v>45658</v>
       </c>
       <c r="D238">
         <v>2025</v>
       </c>
-      <c r="E238" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F238" s="1" t="s">
+      <c r="E238" t="s">
+        <v>9</v>
+      </c>
+      <c r="F238" t="s">
         <v>10</v>
       </c>
       <c r="G238">
@@ -13195,19 +13120,19 @@
       <c r="A239">
         <v>3</v>
       </c>
-      <c r="B239" s="1" t="s">
+      <c r="B239" t="s">
         <v>15</v>
       </c>
-      <c r="C239" s="2">
+      <c r="C239" s="1">
         <v>45658</v>
       </c>
       <c r="D239">
         <v>2025</v>
       </c>
-      <c r="E239" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F239" s="1" t="s">
+      <c r="E239" t="s">
+        <v>9</v>
+      </c>
+      <c r="F239" t="s">
         <v>11</v>
       </c>
       <c r="G239">
@@ -13221,19 +13146,19 @@
       <c r="A240">
         <v>3</v>
       </c>
-      <c r="B240" s="1" t="s">
+      <c r="B240" t="s">
         <v>15</v>
       </c>
-      <c r="C240" s="2">
+      <c r="C240" s="1">
         <v>45658</v>
       </c>
       <c r="D240">
         <v>2025</v>
       </c>
-      <c r="E240" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F240" s="1" t="s">
+      <c r="E240" t="s">
+        <v>9</v>
+      </c>
+      <c r="F240" t="s">
         <v>12</v>
       </c>
       <c r="G240">
@@ -13247,19 +13172,19 @@
       <c r="A241">
         <v>3</v>
       </c>
-      <c r="B241" s="1" t="s">
+      <c r="B241" t="s">
         <v>15</v>
       </c>
-      <c r="C241" s="2">
+      <c r="C241" s="1">
         <v>46023</v>
       </c>
       <c r="D241">
         <v>2026</v>
       </c>
-      <c r="E241" s="1" t="s">
+      <c r="E241" t="s">
         <v>13</v>
       </c>
-      <c r="F241" s="1" t="s">
+      <c r="F241" t="s">
         <v>10</v>
       </c>
       <c r="G241">
@@ -13273,19 +13198,19 @@
       <c r="A242">
         <v>3</v>
       </c>
-      <c r="B242" s="1" t="s">
+      <c r="B242" t="s">
         <v>15</v>
       </c>
-      <c r="C242" s="2">
+      <c r="C242" s="1">
         <v>46023</v>
       </c>
       <c r="D242">
         <v>2026</v>
       </c>
-      <c r="E242" s="1" t="s">
+      <c r="E242" t="s">
         <v>13</v>
       </c>
-      <c r="F242" s="1" t="s">
+      <c r="F242" t="s">
         <v>11</v>
       </c>
       <c r="G242">
@@ -13299,19 +13224,19 @@
       <c r="A243">
         <v>3</v>
       </c>
-      <c r="B243" s="1" t="s">
+      <c r="B243" t="s">
         <v>15</v>
       </c>
-      <c r="C243" s="2">
+      <c r="C243" s="1">
         <v>46023</v>
       </c>
       <c r="D243">
         <v>2026</v>
       </c>
-      <c r="E243" s="1" t="s">
+      <c r="E243" t="s">
         <v>13</v>
       </c>
-      <c r="F243" s="1" t="s">
+      <c r="F243" t="s">
         <v>12</v>
       </c>
       <c r="G243">
@@ -13331,7 +13256,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B34FCAFD-884B-45E6-B9ED-1FC8E6D8E398}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" bestFit="1" customWidth="1"/>
@@ -13342,7 +13267,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -13353,7 +13278,7 @@
       <c r="H1" s="6"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -13361,15 +13286,15 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="B4" s="2" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B5">
@@ -13390,112 +13315,74 @@
       <c r="G5">
         <v>2026</v>
       </c>
-      <c r="H5" t="s">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="7">
+        <v>34</v>
+      </c>
+      <c r="C6" s="7">
+        <v>30</v>
+      </c>
+      <c r="D6" s="7">
+        <v>15</v>
+      </c>
+      <c r="E6" s="7">
+        <v>7</v>
+      </c>
+      <c r="F6" s="7">
+        <v>11</v>
+      </c>
+      <c r="G6" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="7">
+        <v>24</v>
+      </c>
+      <c r="C7" s="7">
+        <v>27</v>
+      </c>
+      <c r="D7" s="7">
+        <v>32</v>
+      </c>
+      <c r="E7" s="7">
+        <v>36</v>
+      </c>
+      <c r="F7" s="7">
+        <v>29</v>
+      </c>
+      <c r="G7" s="7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="7">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1">
-        <v>34</v>
-      </c>
-      <c r="C6" s="1">
-        <v>30</v>
-      </c>
-      <c r="D6" s="1">
-        <v>15</v>
-      </c>
-      <c r="E6" s="1">
-        <v>7</v>
-      </c>
-      <c r="F6" s="1">
-        <v>11</v>
-      </c>
-      <c r="G6" s="1">
-        <v>8</v>
-      </c>
-      <c r="H6" s="1">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="1">
-        <v>24</v>
-      </c>
-      <c r="C7" s="1">
-        <v>27</v>
-      </c>
-      <c r="D7" s="1">
-        <v>32</v>
-      </c>
-      <c r="E7" s="1">
-        <v>36</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="C8" s="7">
+        <v>18</v>
+      </c>
+      <c r="D8" s="7">
+        <v>22</v>
+      </c>
+      <c r="E8" s="7">
+        <v>26</v>
+      </c>
+      <c r="F8" s="7">
+        <v>31</v>
+      </c>
+      <c r="G8" s="7">
         <v>29</v>
-      </c>
-      <c r="G7" s="1">
-        <v>22</v>
-      </c>
-      <c r="H7" s="1">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="1">
-        <v>21</v>
-      </c>
-      <c r="C8" s="1">
-        <v>18</v>
-      </c>
-      <c r="D8" s="1">
-        <v>22</v>
-      </c>
-      <c r="E8" s="1">
-        <v>26</v>
-      </c>
-      <c r="F8" s="1">
-        <v>31</v>
-      </c>
-      <c r="G8" s="1">
-        <v>29</v>
-      </c>
-      <c r="H8" s="1">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="1">
-        <v>79</v>
-      </c>
-      <c r="C9" s="1">
-        <v>75</v>
-      </c>
-      <c r="D9" s="1">
-        <v>69</v>
-      </c>
-      <c r="E9" s="1">
-        <v>69</v>
-      </c>
-      <c r="F9" s="1">
-        <v>71</v>
-      </c>
-      <c r="G9" s="1">
-        <v>59</v>
-      </c>
-      <c r="H9" s="1">
-        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -13548,10 +13435,10 @@
       <c r="A2">
         <v>2021</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
         <v>10</v>
       </c>
       <c r="D2">
@@ -13571,10 +13458,10 @@
       <c r="A3">
         <v>2021</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
         <v>11</v>
       </c>
       <c r="D3">
@@ -13594,10 +13481,10 @@
       <c r="A4">
         <v>2021</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
         <v>12</v>
       </c>
       <c r="D4">
@@ -13617,10 +13504,10 @@
       <c r="A5">
         <v>2022</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
         <v>10</v>
       </c>
       <c r="D5">
@@ -13640,10 +13527,10 @@
       <c r="A6">
         <v>2022</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
         <v>11</v>
       </c>
       <c r="D6">
@@ -13663,10 +13550,10 @@
       <c r="A7">
         <v>2022</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
         <v>12</v>
       </c>
       <c r="D7">
@@ -13686,10 +13573,10 @@
       <c r="A8">
         <v>2023</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
         <v>10</v>
       </c>
       <c r="D8">
@@ -13709,10 +13596,10 @@
       <c r="A9">
         <v>2023</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
         <v>11</v>
       </c>
       <c r="D9">
@@ -13732,10 +13619,10 @@
       <c r="A10">
         <v>2023</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
         <v>12</v>
       </c>
       <c r="D10">
@@ -13755,10 +13642,10 @@
       <c r="A11">
         <v>2024</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
         <v>10</v>
       </c>
       <c r="D11">
@@ -13778,10 +13665,10 @@
       <c r="A12">
         <v>2024</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
         <v>11</v>
       </c>
       <c r="D12">
@@ -13801,10 +13688,10 @@
       <c r="A13">
         <v>2024</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
         <v>12</v>
       </c>
       <c r="D13">
@@ -13824,10 +13711,10 @@
       <c r="A14">
         <v>2025</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
         <v>10</v>
       </c>
       <c r="D14">
@@ -13847,10 +13734,10 @@
       <c r="A15">
         <v>2025</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
         <v>11</v>
       </c>
       <c r="D15">
@@ -13870,10 +13757,10 @@
       <c r="A16">
         <v>2025</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="1" t="s">
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
         <v>12</v>
       </c>
       <c r="D16">
@@ -13893,10 +13780,10 @@
       <c r="A17">
         <v>2026</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" t="s">
         <v>10</v>
       </c>
       <c r="D17">
@@ -13916,10 +13803,10 @@
       <c r="A18">
         <v>2026</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>11</v>
       </c>
       <c r="D18">
@@ -13939,10 +13826,10 @@
       <c r="A19">
         <v>2026</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" t="s">
         <v>12</v>
       </c>
       <c r="D19">
@@ -13971,55 +13858,53 @@
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="1" max="1" width="56.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="B3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3"/>
+    </row>
+    <row r="4" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>2021</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>2022</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <v>2023</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>2024</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="4">
         <v>2025</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <v>2026</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="H4"/>
+    </row>
+    <row r="5" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="8">
@@ -14040,12 +13925,10 @@
       <c r="G5" s="8">
         <v>8</v>
       </c>
-      <c r="H5" s="8">
-        <v>59.75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="H5"/>
+    </row>
+    <row r="6" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="8">
@@ -14066,12 +13949,10 @@
       <c r="G6" s="8">
         <v>11</v>
       </c>
-      <c r="H6" s="8">
-        <v>64.28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="H6"/>
+    </row>
+    <row r="7" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="8">
@@ -14092,35 +13973,17 @@
       <c r="G7" s="8">
         <v>8.83</v>
       </c>
-      <c r="H7" s="8">
-        <v>61.66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="8">
-        <v>33.5</v>
-      </c>
-      <c r="C8" s="8">
-        <v>32.25</v>
-      </c>
-      <c r="D8" s="8">
-        <v>30.85</v>
-      </c>
-      <c r="E8" s="8">
-        <v>29.159999999999997</v>
-      </c>
-      <c r="F8" s="8">
-        <v>32.1</v>
-      </c>
-      <c r="G8" s="8">
-        <v>27.83</v>
-      </c>
-      <c r="H8" s="8">
-        <v>185.69</v>
-      </c>
+      <c r="H7"/>
+    </row>
+    <row r="8" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8"/>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
